--- a/Apolo/Assets/Excel/Template.xlsx
+++ b/Apolo/Assets/Excel/Template.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aruiz\source\repos\alexruizdev\Apolo\Apolo\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD3C5EA-C620-487D-86F3-B8E7E72EA1CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{495D0400-2F68-4BE7-97BA-F257A656FF75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="19440" windowHeight="14880" activeTab="1" xr2:uid="{AC1E564E-6DB8-4849-BF2A-83F157C7F386}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{AC1E564E-6DB8-4849-BF2A-83F157C7F386}"/>
   </bookViews>
   <sheets>
-    <sheet name="Lessons" sheetId="1" r:id="rId1"/>
-    <sheet name="Invoices" sheetId="3" r:id="rId2"/>
+    <sheet name="Services" sheetId="8" r:id="rId1"/>
+    <sheet name="Payers" sheetId="7" r:id="rId2"/>
     <sheet name="Students" sheetId="4" r:id="rId3"/>
     <sheet name="Specifications" sheetId="5" r:id="rId4"/>
-    <sheet name="Payers" sheetId="7" r:id="rId5"/>
-    <sheet name="Services" sheetId="8" r:id="rId6"/>
+    <sheet name="Lessons" sheetId="1" r:id="rId5"/>
+    <sheet name="Invoices" sheetId="3" r:id="rId6"/>
     <sheet name="Profiles" sheetId="9" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="45">
   <si>
     <t>Lessons</t>
   </si>
@@ -123,9 +123,6 @@
   </si>
   <si>
     <t>Last name</t>
-  </si>
-  <si>
-    <t>Commute</t>
   </si>
   <si>
     <t>Specifications</t>
@@ -498,25 +495,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="84">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
+  <dxfs count="83">
     <dxf>
       <font>
         <strike val="0"/>
@@ -1274,19 +1253,6 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -1407,46 +1373,277 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="3" tint="0.249977111117893"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="3" tint="0.249977111117893"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="3" tint="0.24994659260841701"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="3" tint="0.249977111117893"/>
+        </left>
+        <right style="thin">
+          <color theme="3" tint="0.249977111117893"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1566,219 +1763,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="3" tint="0.249977111117893"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="3" tint="0.249977111117893"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="6"/>
-          <bgColor theme="3" tint="0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="3" tint="0.249977111117893"/>
-        </left>
-        <right style="thin">
-          <color theme="3" tint="0.249977111117893"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1793,119 +1777,118 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}" name="Lessons" displayName="Lessons" ref="B5:M6" insertRow="1" totalsRowShown="0" headerRowDxfId="83" dataDxfId="81" headerRowBorderDxfId="82" tableBorderDxfId="80">
-  <autoFilter ref="B5:M6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{C1CFA75B-DE21-4250-99D5-6D2B34197E9D}" name="Date" dataDxfId="79"/>
-    <tableColumn id="3" xr3:uid="{E13660C3-AD05-4CF3-9631-AE40C9F89101}" name="Student" dataDxfId="78"/>
-    <tableColumn id="4" xr3:uid="{18BEE297-19DF-4B3B-B4FD-CFAE8F7A6949}" name="Service" dataDxfId="77"/>
-    <tableColumn id="5" xr3:uid="{6CA1B731-8C2F-4DA6-B472-EE33DF6113CD}" name="Duration (min)" dataDxfId="76"/>
-    <tableColumn id="6" xr3:uid="{7DCD903B-2C97-4AD2-B1F7-E4B6242A2CC8}" name="Online" dataDxfId="75"/>
-    <tableColumn id="7" xr3:uid="{96F08C18-13F5-448F-99C8-A2B2DE97A9B4}" name="Is total price" dataDxfId="74"/>
-    <tableColumn id="8" xr3:uid="{7A134DA8-4763-4978-90B3-711AAD8B520E}" name="Price per student" dataDxfId="73"/>
-    <tableColumn id="9" xr3:uid="{0350D2EA-6D0F-4D17-BF70-FFF762F354F0}" name="Paid" dataDxfId="72"/>
-    <tableColumn id="10" xr3:uid="{08B3198D-C1DC-4D8E-A4DE-7250D3A7C710}" name="Lesson ID" dataDxfId="71"/>
-    <tableColumn id="11" xr3:uid="{D13F67C3-A32E-454C-AE4D-C716888F27CB}" name="Attendance ID" dataDxfId="70"/>
-    <tableColumn id="12" xr3:uid="{9B183B96-B338-4F28-AD14-AC6E651B6858}" name="Student ID" dataDxfId="69"/>
-    <tableColumn id="13" xr3:uid="{05AE8549-9E32-42AB-9E0E-0BECB84ADE19}" name="Service ID" dataDxfId="68"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C0795F78-0156-4685-AF9B-C080EB165C86}" name="Services" displayName="Services" ref="B5:D6" insertRow="1" totalsRowShown="0" headerRowDxfId="20" dataDxfId="18" headerRowBorderDxfId="19" tableBorderDxfId="17">
+  <autoFilter ref="B5:D6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{0421A27A-273F-4193-83E8-232DCB727B04}" name="Name" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{322E168C-94B6-4464-82B7-AE5BD1C86BBE}" name="Price / h" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{699229C5-F45C-42AE-B09B-A008CEFA4B73}" name="ID" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C992FC1D-929F-4FCC-8034-BD1DE7AB4724}" name="Invoices" displayName="Invoices" ref="B5:J6" insertRow="1" totalsRowShown="0" headerRowDxfId="67" dataDxfId="65" headerRowBorderDxfId="66" tableBorderDxfId="64">
-  <autoFilter ref="B5:J6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{C69805C5-2DE6-4F5E-8595-BD91192122FB}" name="ID" dataDxfId="63"/>
-    <tableColumn id="2" xr3:uid="{31887EF0-F959-496C-8E82-BFC9313A5BD4}" name="Name" dataDxfId="62"/>
-    <tableColumn id="3" xr3:uid="{BD335C6E-9933-48E1-94D0-D0E510EFF5FB}" name="Created UTC" dataDxfId="61"/>
-    <tableColumn id="4" xr3:uid="{899EB7AE-2A40-41FC-80B1-65CB3A3ADF6E}" name="Payer name" dataDxfId="60"/>
-    <tableColumn id="5" xr3:uid="{3309E227-DE1E-43C5-A6B6-0EC92AFFC66E}" name="Student" dataDxfId="0"/>
-    <tableColumn id="6" xr3:uid="{BB6B6371-F4F3-4ED2-B36B-8B9F19FEC62D}" name="Total" dataDxfId="59"/>
-    <tableColumn id="8" xr3:uid="{BC748279-6F8A-40CD-A73A-4EAEC24A6408}" name="Paid" dataDxfId="58"/>
-    <tableColumn id="12" xr3:uid="{8DFC1E1F-49ED-490A-A022-750D97F2DB5E}" name="Payer ID" dataDxfId="57"/>
-    <tableColumn id="13" xr3:uid="{B0BEC736-D1AC-4A3A-A050-D3DA3F256C81}" name="Line ID" dataDxfId="56"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0A79F4B1-F900-45BC-9D44-285E808E7870}" name="Payers" displayName="Payers" ref="B5:H6" insertRow="1" totalsRowShown="0" headerRowDxfId="31" dataDxfId="29" headerRowBorderDxfId="30" tableBorderDxfId="28">
+  <autoFilter ref="B5:H6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{5BA77401-135F-49A0-9018-51E3A0234CED}" name="First name" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{EDB180AC-1296-443F-B84C-4D4EE4AE073B}" name="Last name" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{DCE1ACAA-6DAD-4705-81EB-7DFA2DF001BC}" name="Address" dataDxfId="25"/>
+    <tableColumn id="14" xr3:uid="{5B929BF7-C179-40AD-A842-4DFB12038777}" name="Zip code" dataDxfId="24"/>
+    <tableColumn id="15" xr3:uid="{6D6E1C47-E3A4-4383-BEC9-B9EAA078358A}" name="City" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{932DDB97-98FA-4056-8148-3C1EBD8A6957}" name="NIF/CIF" dataDxfId="22"/>
+    <tableColumn id="10" xr3:uid="{E234FAE6-CB9B-4EA0-B055-27B95F566BDE}" name="ID" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{921EB506-3A8A-4A0B-B4FB-962E1B230FC8}" name="Students" displayName="Students" ref="B5:G6" insertRow="1" totalsRowShown="0" headerRowDxfId="55" dataDxfId="53" headerRowBorderDxfId="54" tableBorderDxfId="52">
-  <autoFilter ref="B5:G6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
-  <tableColumns count="6">
-    <tableColumn id="2" xr3:uid="{D3B37E7D-9062-40D6-B2B2-0A50D2AF30D8}" name="First name" dataDxfId="51"/>
-    <tableColumn id="3" xr3:uid="{DA765E80-CB03-496C-AB85-04C12F7F6EA1}" name="Last name" dataDxfId="50"/>
-    <tableColumn id="14" xr3:uid="{59DCAFC2-89B1-4CB1-9CF4-2945D31AD0A7}" name="Payer name" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{4CABC10F-1A7F-4D86-B90B-E069B2B53969}" name="Commute" dataDxfId="48"/>
-    <tableColumn id="10" xr3:uid="{1186A2E8-3B8B-4232-BAAC-F12E28103DE4}" name="Id" dataDxfId="47"/>
-    <tableColumn id="11" xr3:uid="{2C87B7EC-1CBC-4BF1-BC1B-A80BEE6DF561}" name="PayerId" dataDxfId="46"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{921EB506-3A8A-4A0B-B4FB-962E1B230FC8}" name="Students" displayName="Students" ref="B5:F6" insertRow="1" totalsRowShown="0" headerRowDxfId="53" dataDxfId="51" headerRowBorderDxfId="52" tableBorderDxfId="50">
+  <autoFilter ref="B5:F6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
+  <tableColumns count="5">
+    <tableColumn id="2" xr3:uid="{D3B37E7D-9062-40D6-B2B2-0A50D2AF30D8}" name="First name" dataDxfId="49"/>
+    <tableColumn id="3" xr3:uid="{DA765E80-CB03-496C-AB85-04C12F7F6EA1}" name="Last name" dataDxfId="48"/>
+    <tableColumn id="14" xr3:uid="{59DCAFC2-89B1-4CB1-9CF4-2945D31AD0A7}" name="Payer name" dataDxfId="47"/>
+    <tableColumn id="10" xr3:uid="{1186A2E8-3B8B-4232-BAAC-F12E28103DE4}" name="Id" dataDxfId="46"/>
+    <tableColumn id="11" xr3:uid="{2C87B7EC-1CBC-4BF1-BC1B-A80BEE6DF561}" name="PayerId" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AD4BFF54-6050-4EA0-B5EE-4251BB923ED8}" name="Specifications" displayName="Specifications" ref="B5:J6" insertRow="1" totalsRowShown="0" headerRowDxfId="45" dataDxfId="43" headerRowBorderDxfId="44" tableBorderDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AD4BFF54-6050-4EA0-B5EE-4251BB923ED8}" name="Specifications" displayName="Specifications" ref="B5:J6" insertRow="1" totalsRowShown="0" headerRowDxfId="44" dataDxfId="42" headerRowBorderDxfId="43" tableBorderDxfId="41">
   <autoFilter ref="B5:J6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{A984BEB5-CD0A-4CBC-8261-5202F875C894}" name="Name" dataDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{E5D86B37-BC1B-421B-8F67-1924F653B36B}" name="Student name" dataDxfId="40"/>
-    <tableColumn id="3" xr3:uid="{4F31CB14-2A08-4670-A72E-704E0461B7C0}" name="Service" dataDxfId="39"/>
-    <tableColumn id="14" xr3:uid="{2046F612-0B54-4B4A-8FFD-EC5D6AB309E9}" name="Duration" dataDxfId="38"/>
-    <tableColumn id="15" xr3:uid="{3B56031F-69EE-48E1-914B-517D98BD2AF6}" name="Price" dataDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{E7ED6501-C9FE-4D56-95A1-F6238FF1D18F}" name="Online" dataDxfId="36"/>
-    <tableColumn id="10" xr3:uid="{AC948A85-76D1-41F8-8643-7143CFC6B853}" name="ID" dataDxfId="35"/>
-    <tableColumn id="16" xr3:uid="{97831813-DA71-41F9-9C8D-B5BDF0ABEBAF}" name="Service ID" dataDxfId="34"/>
-    <tableColumn id="11" xr3:uid="{CF31A15E-2BAA-48FB-B0FE-4AE64ECEA47C}" name="Student ID" dataDxfId="33"/>
+    <tableColumn id="1" xr3:uid="{A984BEB5-CD0A-4CBC-8261-5202F875C894}" name="Name" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{E5D86B37-BC1B-421B-8F67-1924F653B36B}" name="Student name" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{4F31CB14-2A08-4670-A72E-704E0461B7C0}" name="Service" dataDxfId="38"/>
+    <tableColumn id="14" xr3:uid="{2046F612-0B54-4B4A-8FFD-EC5D6AB309E9}" name="Duration" dataDxfId="37"/>
+    <tableColumn id="15" xr3:uid="{3B56031F-69EE-48E1-914B-517D98BD2AF6}" name="Price" dataDxfId="36"/>
+    <tableColumn id="4" xr3:uid="{E7ED6501-C9FE-4D56-95A1-F6238FF1D18F}" name="Online" dataDxfId="35"/>
+    <tableColumn id="10" xr3:uid="{AC948A85-76D1-41F8-8643-7143CFC6B853}" name="ID" dataDxfId="34"/>
+    <tableColumn id="16" xr3:uid="{97831813-DA71-41F9-9C8D-B5BDF0ABEBAF}" name="Service ID" dataDxfId="33"/>
+    <tableColumn id="11" xr3:uid="{CF31A15E-2BAA-48FB-B0FE-4AE64ECEA47C}" name="Student ID" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0A79F4B1-F900-45BC-9D44-285E808E7870}" name="Payers" displayName="Payers" ref="B5:H6" insertRow="1" totalsRowShown="0" headerRowDxfId="32" dataDxfId="30" headerRowBorderDxfId="31" tableBorderDxfId="29">
-  <autoFilter ref="B5:H6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{5BA77401-135F-49A0-9018-51E3A0234CED}" name="First name" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{EDB180AC-1296-443F-B84C-4D4EE4AE073B}" name="Last name" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{DCE1ACAA-6DAD-4705-81EB-7DFA2DF001BC}" name="Address" dataDxfId="26"/>
-    <tableColumn id="14" xr3:uid="{5B929BF7-C179-40AD-A842-4DFB12038777}" name="Zip code" dataDxfId="25"/>
-    <tableColumn id="15" xr3:uid="{6D6E1C47-E3A4-4383-BEC9-B9EAA078358A}" name="City" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{932DDB97-98FA-4056-8148-3C1EBD8A6957}" name="NIF/CIF" dataDxfId="23"/>
-    <tableColumn id="10" xr3:uid="{E234FAE6-CB9B-4EA0-B055-27B95F566BDE}" name="ID" dataDxfId="22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}" name="Lessons" displayName="Lessons" ref="B5:M6" insertRow="1" totalsRowShown="0" headerRowDxfId="69" dataDxfId="67" headerRowBorderDxfId="68" tableBorderDxfId="66">
+  <autoFilter ref="B5:M6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{C1CFA75B-DE21-4250-99D5-6D2B34197E9D}" name="Date" dataDxfId="65"/>
+    <tableColumn id="3" xr3:uid="{E13660C3-AD05-4CF3-9631-AE40C9F89101}" name="Student" dataDxfId="64"/>
+    <tableColumn id="4" xr3:uid="{18BEE297-19DF-4B3B-B4FD-CFAE8F7A6949}" name="Service" dataDxfId="63"/>
+    <tableColumn id="5" xr3:uid="{6CA1B731-8C2F-4DA6-B472-EE33DF6113CD}" name="Duration (min)" dataDxfId="62"/>
+    <tableColumn id="6" xr3:uid="{7DCD903B-2C97-4AD2-B1F7-E4B6242A2CC8}" name="Online" dataDxfId="61"/>
+    <tableColumn id="7" xr3:uid="{96F08C18-13F5-448F-99C8-A2B2DE97A9B4}" name="Is total price" dataDxfId="60"/>
+    <tableColumn id="8" xr3:uid="{7A134DA8-4763-4978-90B3-711AAD8B520E}" name="Price per student" dataDxfId="59"/>
+    <tableColumn id="9" xr3:uid="{0350D2EA-6D0F-4D17-BF70-FFF762F354F0}" name="Paid" dataDxfId="58"/>
+    <tableColumn id="10" xr3:uid="{08B3198D-C1DC-4D8E-A4DE-7250D3A7C710}" name="Lesson ID" dataDxfId="57"/>
+    <tableColumn id="11" xr3:uid="{D13F67C3-A32E-454C-AE4D-C716888F27CB}" name="Attendance ID" dataDxfId="56"/>
+    <tableColumn id="12" xr3:uid="{9B183B96-B338-4F28-AD14-AC6E651B6858}" name="Student ID" dataDxfId="55"/>
+    <tableColumn id="13" xr3:uid="{05AE8549-9E32-42AB-9E0E-0BECB84ADE19}" name="Service ID" dataDxfId="54"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C0795F78-0156-4685-AF9B-C080EB165C86}" name="Services" displayName="Services" ref="B5:D6" insertRow="1" totalsRowShown="0" headerRowDxfId="21" dataDxfId="19" headerRowBorderDxfId="20" tableBorderDxfId="18">
-  <autoFilter ref="B5:D6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0421A27A-273F-4193-83E8-232DCB727B04}" name="Name" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{322E168C-94B6-4464-82B7-AE5BD1C86BBE}" name="Price / h" dataDxfId="16"/>
-    <tableColumn id="10" xr3:uid="{699229C5-F45C-42AE-B09B-A008CEFA4B73}" name="ID" dataDxfId="15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C992FC1D-929F-4FCC-8034-BD1DE7AB4724}" name="Invoices" displayName="Invoices" ref="B5:J6" insertRow="1" totalsRowShown="0" headerRowDxfId="82" dataDxfId="80" headerRowBorderDxfId="81" tableBorderDxfId="79">
+  <autoFilter ref="B5:J6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{C69805C5-2DE6-4F5E-8595-BD91192122FB}" name="ID" dataDxfId="78"/>
+    <tableColumn id="2" xr3:uid="{31887EF0-F959-496C-8E82-BFC9313A5BD4}" name="Name" dataDxfId="77"/>
+    <tableColumn id="3" xr3:uid="{BD335C6E-9933-48E1-94D0-D0E510EFF5FB}" name="Created UTC" dataDxfId="76"/>
+    <tableColumn id="4" xr3:uid="{899EB7AE-2A40-41FC-80B1-65CB3A3ADF6E}" name="Payer name" dataDxfId="75"/>
+    <tableColumn id="5" xr3:uid="{3309E227-DE1E-43C5-A6B6-0EC92AFFC66E}" name="Student" dataDxfId="74"/>
+    <tableColumn id="6" xr3:uid="{BB6B6371-F4F3-4ED2-B36B-8B9F19FEC62D}" name="Total" dataDxfId="73"/>
+    <tableColumn id="8" xr3:uid="{BC748279-6F8A-40CD-A73A-4EAEC24A6408}" name="Paid" dataDxfId="72"/>
+    <tableColumn id="12" xr3:uid="{8DFC1E1F-49ED-490A-A022-750D97F2DB5E}" name="Payer ID" dataDxfId="71"/>
+    <tableColumn id="13" xr3:uid="{B0BEC736-D1AC-4A3A-A050-D3DA3F256C81}" name="Line ID" dataDxfId="70"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A2CA2C87-2B1E-47CC-B98B-F6DB30254282}" name="Profiles" displayName="Profiles" ref="B5:K6" insertRow="1" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A2CA2C87-2B1E-47CC-B98B-F6DB30254282}" name="Profiles" displayName="Profiles" ref="B5:K6" insertRow="1" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10">
   <autoFilter ref="B5:K6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{2F7003BC-BC4F-49D1-8191-9B7B77A95DAD}" name="Full name" dataDxfId="10"/>
-    <tableColumn id="17" xr3:uid="{1ED8C0D8-B8BF-4CB8-BF2A-11954C2F7E1C}" name="Zip code" dataDxfId="9"/>
-    <tableColumn id="20" xr3:uid="{7DBD046D-D51C-4C4F-8604-D6DEC2103E43}" name="City" dataDxfId="8"/>
-    <tableColumn id="19" xr3:uid="{7D393146-6466-4F51-87B6-10B7C5614A6A}" name="Phone" dataDxfId="7"/>
-    <tableColumn id="18" xr3:uid="{C771F655-E405-4BB5-AD39-3D5A94E1BBE0}" name="CIF/NIF" dataDxfId="6"/>
-    <tableColumn id="23" xr3:uid="{0F800687-A552-4911-A84F-66F27E40B2E9}" name="Email" dataDxfId="5"/>
-    <tableColumn id="22" xr3:uid="{2B05B060-5CA2-4293-8190-C4310A9D436E}" name="Bank name" dataDxfId="4"/>
-    <tableColumn id="21" xr3:uid="{7D5301B1-5635-4EF9-88C0-B2D2B15286FD}" name="Bank account" dataDxfId="3"/>
-    <tableColumn id="24" xr3:uid="{9790EA57-CF62-4EF2-ACAE-3D1545D8BFD5}" name="IVA" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{FAC1AFDA-6CB4-4B8D-A36E-7D10AC1588CA}" name="Address" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{2F7003BC-BC4F-49D1-8191-9B7B77A95DAD}" name="Full name" dataDxfId="9"/>
+    <tableColumn id="17" xr3:uid="{1ED8C0D8-B8BF-4CB8-BF2A-11954C2F7E1C}" name="Zip code" dataDxfId="8"/>
+    <tableColumn id="20" xr3:uid="{7DBD046D-D51C-4C4F-8604-D6DEC2103E43}" name="City" dataDxfId="7"/>
+    <tableColumn id="19" xr3:uid="{7D393146-6466-4F51-87B6-10B7C5614A6A}" name="Phone" dataDxfId="6"/>
+    <tableColumn id="18" xr3:uid="{C771F655-E405-4BB5-AD39-3D5A94E1BBE0}" name="CIF/NIF" dataDxfId="5"/>
+    <tableColumn id="23" xr3:uid="{0F800687-A552-4911-A84F-66F27E40B2E9}" name="Email" dataDxfId="4"/>
+    <tableColumn id="22" xr3:uid="{2B05B060-5CA2-4293-8190-C4310A9D436E}" name="Bank name" dataDxfId="3"/>
+    <tableColumn id="21" xr3:uid="{7D5301B1-5635-4EF9-88C0-B2D2B15286FD}" name="Bank account" dataDxfId="2"/>
+    <tableColumn id="24" xr3:uid="{9790EA57-CF62-4EF2-ACAE-3D1545D8BFD5}" name="IVA" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{FAC1AFDA-6CB4-4B8D-A36E-7D10AC1588CA}" name="Address" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2227,6 +2210,350 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{349C6D3A-2581-4BC1-B198-043D81DE2DED}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="29.140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+    </row>
+    <row r="3" spans="1:5" ht="34.5" x14ac:dyDescent="0.45">
+      <c r="B3" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="20"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4"/>
+      <c r="B5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="14"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B3:C3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD90C9EB-D6B8-4999-A37E-50FEE41AA263}">
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" style="2" customWidth="1"/>
+    <col min="4" max="6" width="31.28515625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="23.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="60.28515625" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="3" spans="1:9" ht="34.5" x14ac:dyDescent="0.45">
+      <c r="B3" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" spans="1:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4"/>
+      <c r="B5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="4"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="14"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B3:G3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E084E8AE-8C3A-446D-A929-54817F8C0DDF}">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13" style="2" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="31.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="3" spans="1:7" ht="34.5" x14ac:dyDescent="0.45">
+      <c r="B3" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4"/>
+      <c r="B5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="5"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="4"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D59E97CD-50F3-44EA-A57D-8B54153DA60F}">
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13" style="2" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" style="2" customWidth="1"/>
+    <col min="4" max="6" width="31.28515625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="23.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.85546875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="3" spans="1:11" ht="34.5" x14ac:dyDescent="0.45">
+      <c r="B3" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+    </row>
+    <row r="5" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4"/>
+      <c r="B5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" s="5"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="4"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="7"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B3:G3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B8EF7-62DE-4FCD-B8E3-460BB4D2C6F0}">
   <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -2361,7 +2688,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BEF98F2-4AC5-4AA1-85C9-545C3E11603A}">
   <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -2428,10 +2755,10 @@
         <v>10</v>
       </c>
       <c r="I5" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" s="15" t="s">
         <v>44</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>45</v>
       </c>
       <c r="K5" s="5"/>
     </row>
@@ -2459,358 +2786,6 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B3:G3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E084E8AE-8C3A-446D-A929-54817F8C0DDF}">
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="7.140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="13" style="2" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" style="2" customWidth="1"/>
-    <col min="4" max="5" width="31.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="23.7109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="3" spans="1:8" ht="34.5" x14ac:dyDescent="0.45">
-      <c r="B3" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
-      <c r="B5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="5"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="4"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="7"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B3:F3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D59E97CD-50F3-44EA-A57D-8B54153DA60F}">
-  <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="7.140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="13" style="2" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" style="2" customWidth="1"/>
-    <col min="4" max="6" width="31.28515625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="23.7109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.85546875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="3" spans="1:11" ht="34.5" x14ac:dyDescent="0.45">
-      <c r="B3" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
-      <c r="B5" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="5"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="4"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="7"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B3:G3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD90C9EB-D6B8-4999-A37E-50FEE41AA263}">
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="7.140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" style="2" customWidth="1"/>
-    <col min="4" max="6" width="31.28515625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="23.7109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="60.28515625" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="3" spans="1:9" ht="34.5" x14ac:dyDescent="0.45">
-      <c r="B3" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
-      <c r="B5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="5"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="4"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="14"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B3:G3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{349C6D3A-2581-4BC1-B198-043D81DE2DED}">
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="7.140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="29.140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="3" spans="1:5" ht="34.5" x14ac:dyDescent="0.45">
-      <c r="B3" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="20"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
-      <c r="B5" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="5"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="14"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B3:C3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -2844,7 +2819,7 @@
     </row>
     <row r="3" spans="1:12" ht="34.5" x14ac:dyDescent="0.45">
       <c r="B3" s="19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -2871,34 +2846,34 @@
     <row r="5" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="I5" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="J5" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="J5" s="6" t="s">
-        <v>43</v>
-      </c>
       <c r="K5" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L5" s="5"/>
     </row>

--- a/Apolo/Assets/Excel/Template.xlsx
+++ b/Apolo/Assets/Excel/Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aruiz\source\repos\alexruizdev\Apolo\Apolo\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{495D0400-2F68-4BE7-97BA-F257A656FF75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C3D36C-BF27-4BF0-B46E-5AD1FE48286B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{AC1E564E-6DB8-4849-BF2A-83F157C7F386}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="19440" windowHeight="14880" activeTab="6" xr2:uid="{AC1E564E-6DB8-4849-BF2A-83F157C7F386}"/>
   </bookViews>
   <sheets>
     <sheet name="Services" sheetId="8" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="50">
   <si>
     <t>Lessons</t>
   </si>
@@ -71,9 +71,6 @@
     <t>Online</t>
   </si>
   <si>
-    <t>Is total price</t>
-  </si>
-  <si>
     <t>Price per student</t>
   </si>
   <si>
@@ -180,6 +177,24 @@
   </si>
   <si>
     <t>Line ID</t>
+  </si>
+  <si>
+    <t>Weekend</t>
+  </si>
+  <si>
+    <t>Price / hour</t>
+  </si>
+  <si>
+    <t>Travel allowance</t>
+  </si>
+  <si>
+    <t>Weekend Fee</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Payer</t>
   </si>
 </sst>
 </file>
@@ -495,7 +510,168 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="83">
+  <dxfs count="88">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -780,6 +956,282 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF215C98"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFFFFFFF"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color theme="5" tint="-0.249977111117893"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="5" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="5" tint="-0.249977111117893"/>
+        </left>
+        <right style="thin">
+          <color theme="5" tint="-0.249977111117893"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top/>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
       <border outline="0">
         <top style="thin">
           <color rgb="FF215C98"/>
@@ -892,38 +1344,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1029,48 +1449,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color theme="0"/>
-        </right>
-        <top/>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1253,38 +1631,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1433,43 +1779,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
@@ -1575,194 +1884,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FF215C98"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFFFFFFF"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color theme="5" tint="-0.249977111117893"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="6"/>
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="5" tint="-0.249977111117893"/>
-        </left>
-        <right style="thin">
-          <color theme="5" tint="-0.249977111117893"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1777,118 +1898,123 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C0795F78-0156-4685-AF9B-C080EB165C86}" name="Services" displayName="Services" ref="B5:D6" insertRow="1" totalsRowShown="0" headerRowDxfId="20" dataDxfId="18" headerRowBorderDxfId="19" tableBorderDxfId="17">
-  <autoFilter ref="B5:D6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0421A27A-273F-4193-83E8-232DCB727B04}" name="Name" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{322E168C-94B6-4464-82B7-AE5BD1C86BBE}" name="Price / h" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{699229C5-F45C-42AE-B09B-A008CEFA4B73}" name="ID" dataDxfId="14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C0795F78-0156-4685-AF9B-C080EB165C86}" name="Services" displayName="Services" ref="B5:E6" insertRow="1" totalsRowShown="0" headerRowDxfId="74" dataDxfId="72" headerRowBorderDxfId="73" tableBorderDxfId="71">
+  <autoFilter ref="B5:E6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{0421A27A-273F-4193-83E8-232DCB727B04}" name="Name" dataDxfId="70"/>
+    <tableColumn id="3" xr3:uid="{F070E4D6-2A8B-4929-BF04-8530F193BF70}" name="Price" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{322E168C-94B6-4464-82B7-AE5BD1C86BBE}" name="Price / h" dataDxfId="69"/>
+    <tableColumn id="10" xr3:uid="{699229C5-F45C-42AE-B09B-A008CEFA4B73}" name="ID" dataDxfId="68"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0A79F4B1-F900-45BC-9D44-285E808E7870}" name="Payers" displayName="Payers" ref="B5:H6" insertRow="1" totalsRowShown="0" headerRowDxfId="31" dataDxfId="29" headerRowBorderDxfId="30" tableBorderDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0A79F4B1-F900-45BC-9D44-285E808E7870}" name="Payers" displayName="Payers" ref="B5:H6" insertRow="1" totalsRowShown="0" headerRowDxfId="67" dataDxfId="65" headerRowBorderDxfId="66" tableBorderDxfId="64">
   <autoFilter ref="B5:H6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{5BA77401-135F-49A0-9018-51E3A0234CED}" name="First name" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{EDB180AC-1296-443F-B84C-4D4EE4AE073B}" name="Last name" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{DCE1ACAA-6DAD-4705-81EB-7DFA2DF001BC}" name="Address" dataDxfId="25"/>
-    <tableColumn id="14" xr3:uid="{5B929BF7-C179-40AD-A842-4DFB12038777}" name="Zip code" dataDxfId="24"/>
-    <tableColumn id="15" xr3:uid="{6D6E1C47-E3A4-4383-BEC9-B9EAA078358A}" name="City" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{932DDB97-98FA-4056-8148-3C1EBD8A6957}" name="NIF/CIF" dataDxfId="22"/>
-    <tableColumn id="10" xr3:uid="{E234FAE6-CB9B-4EA0-B055-27B95F566BDE}" name="ID" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{5BA77401-135F-49A0-9018-51E3A0234CED}" name="First name" dataDxfId="63"/>
+    <tableColumn id="2" xr3:uid="{EDB180AC-1296-443F-B84C-4D4EE4AE073B}" name="Last name" dataDxfId="62"/>
+    <tableColumn id="3" xr3:uid="{DCE1ACAA-6DAD-4705-81EB-7DFA2DF001BC}" name="Address" dataDxfId="61"/>
+    <tableColumn id="14" xr3:uid="{5B929BF7-C179-40AD-A842-4DFB12038777}" name="Zip code" dataDxfId="60"/>
+    <tableColumn id="15" xr3:uid="{6D6E1C47-E3A4-4383-BEC9-B9EAA078358A}" name="City" dataDxfId="59"/>
+    <tableColumn id="4" xr3:uid="{932DDB97-98FA-4056-8148-3C1EBD8A6957}" name="NIF/CIF" dataDxfId="58"/>
+    <tableColumn id="10" xr3:uid="{E234FAE6-CB9B-4EA0-B055-27B95F566BDE}" name="ID" dataDxfId="57"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{921EB506-3A8A-4A0B-B4FB-962E1B230FC8}" name="Students" displayName="Students" ref="B5:F6" insertRow="1" totalsRowShown="0" headerRowDxfId="53" dataDxfId="51" headerRowBorderDxfId="52" tableBorderDxfId="50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{921EB506-3A8A-4A0B-B4FB-962E1B230FC8}" name="Students" displayName="Students" ref="B5:F6" insertRow="1" totalsRowShown="0" headerRowDxfId="56" dataDxfId="54" headerRowBorderDxfId="55" tableBorderDxfId="53">
   <autoFilter ref="B5:F6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{D3B37E7D-9062-40D6-B2B2-0A50D2AF30D8}" name="First name" dataDxfId="49"/>
-    <tableColumn id="3" xr3:uid="{DA765E80-CB03-496C-AB85-04C12F7F6EA1}" name="Last name" dataDxfId="48"/>
-    <tableColumn id="14" xr3:uid="{59DCAFC2-89B1-4CB1-9CF4-2945D31AD0A7}" name="Payer name" dataDxfId="47"/>
-    <tableColumn id="10" xr3:uid="{1186A2E8-3B8B-4232-BAAC-F12E28103DE4}" name="Id" dataDxfId="46"/>
-    <tableColumn id="11" xr3:uid="{2C87B7EC-1CBC-4BF1-BC1B-A80BEE6DF561}" name="PayerId" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{D3B37E7D-9062-40D6-B2B2-0A50D2AF30D8}" name="First name" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{DA765E80-CB03-496C-AB85-04C12F7F6EA1}" name="Last name" dataDxfId="51"/>
+    <tableColumn id="14" xr3:uid="{59DCAFC2-89B1-4CB1-9CF4-2945D31AD0A7}" name="Payer name" dataDxfId="50"/>
+    <tableColumn id="10" xr3:uid="{1186A2E8-3B8B-4232-BAAC-F12E28103DE4}" name="Id" dataDxfId="49"/>
+    <tableColumn id="11" xr3:uid="{2C87B7EC-1CBC-4BF1-BC1B-A80BEE6DF561}" name="PayerId" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AD4BFF54-6050-4EA0-B5EE-4251BB923ED8}" name="Specifications" displayName="Specifications" ref="B5:J6" insertRow="1" totalsRowShown="0" headerRowDxfId="44" dataDxfId="42" headerRowBorderDxfId="43" tableBorderDxfId="41">
-  <autoFilter ref="B5:J6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{A984BEB5-CD0A-4CBC-8261-5202F875C894}" name="Name" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{E5D86B37-BC1B-421B-8F67-1924F653B36B}" name="Student name" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{4F31CB14-2A08-4670-A72E-704E0461B7C0}" name="Service" dataDxfId="38"/>
-    <tableColumn id="14" xr3:uid="{2046F612-0B54-4B4A-8FFD-EC5D6AB309E9}" name="Duration" dataDxfId="37"/>
-    <tableColumn id="15" xr3:uid="{3B56031F-69EE-48E1-914B-517D98BD2AF6}" name="Price" dataDxfId="36"/>
-    <tableColumn id="4" xr3:uid="{E7ED6501-C9FE-4D56-95A1-F6238FF1D18F}" name="Online" dataDxfId="35"/>
-    <tableColumn id="10" xr3:uid="{AC948A85-76D1-41F8-8643-7143CFC6B853}" name="ID" dataDxfId="34"/>
-    <tableColumn id="16" xr3:uid="{97831813-DA71-41F9-9C8D-B5BDF0ABEBAF}" name="Service ID" dataDxfId="33"/>
-    <tableColumn id="11" xr3:uid="{CF31A15E-2BAA-48FB-B0FE-4AE64ECEA47C}" name="Student ID" dataDxfId="32"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AD4BFF54-6050-4EA0-B5EE-4251BB923ED8}" name="Specifications" displayName="Specifications" ref="B5:K6" insertRow="1" totalsRowShown="0" headerRowDxfId="47" dataDxfId="45" headerRowBorderDxfId="46" tableBorderDxfId="44">
+  <autoFilter ref="B5:K6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{A984BEB5-CD0A-4CBC-8261-5202F875C894}" name="Name" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{E5D86B37-BC1B-421B-8F67-1924F653B36B}" name="Student name" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{4F31CB14-2A08-4670-A72E-704E0461B7C0}" name="Service" dataDxfId="41"/>
+    <tableColumn id="14" xr3:uid="{2046F612-0B54-4B4A-8FFD-EC5D6AB309E9}" name="Duration" dataDxfId="40"/>
+    <tableColumn id="15" xr3:uid="{3B56031F-69EE-48E1-914B-517D98BD2AF6}" name="Price" dataDxfId="39"/>
+    <tableColumn id="5" xr3:uid="{4CB3842E-EB1D-45CA-9308-72C92977B251}" name="Online" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{E7ED6501-C9FE-4D56-95A1-F6238FF1D18F}" name="Weekend" dataDxfId="38"/>
+    <tableColumn id="10" xr3:uid="{AC948A85-76D1-41F8-8643-7143CFC6B853}" name="ID" dataDxfId="37"/>
+    <tableColumn id="16" xr3:uid="{97831813-DA71-41F9-9C8D-B5BDF0ABEBAF}" name="Student ID" dataDxfId="36"/>
+    <tableColumn id="11" xr3:uid="{CF31A15E-2BAA-48FB-B0FE-4AE64ECEA47C}" name="Service ID" dataDxfId="35"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}" name="Lessons" displayName="Lessons" ref="B5:M6" insertRow="1" totalsRowShown="0" headerRowDxfId="69" dataDxfId="67" headerRowBorderDxfId="68" tableBorderDxfId="66">
-  <autoFilter ref="B5:M6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{C1CFA75B-DE21-4250-99D5-6D2B34197E9D}" name="Date" dataDxfId="65"/>
-    <tableColumn id="3" xr3:uid="{E13660C3-AD05-4CF3-9631-AE40C9F89101}" name="Student" dataDxfId="64"/>
-    <tableColumn id="4" xr3:uid="{18BEE297-19DF-4B3B-B4FD-CFAE8F7A6949}" name="Service" dataDxfId="63"/>
-    <tableColumn id="5" xr3:uid="{6CA1B731-8C2F-4DA6-B472-EE33DF6113CD}" name="Duration (min)" dataDxfId="62"/>
-    <tableColumn id="6" xr3:uid="{7DCD903B-2C97-4AD2-B1F7-E4B6242A2CC8}" name="Online" dataDxfId="61"/>
-    <tableColumn id="7" xr3:uid="{96F08C18-13F5-448F-99C8-A2B2DE97A9B4}" name="Is total price" dataDxfId="60"/>
-    <tableColumn id="8" xr3:uid="{7A134DA8-4763-4978-90B3-711AAD8B520E}" name="Price per student" dataDxfId="59"/>
-    <tableColumn id="9" xr3:uid="{0350D2EA-6D0F-4D17-BF70-FFF762F354F0}" name="Paid" dataDxfId="58"/>
-    <tableColumn id="10" xr3:uid="{08B3198D-C1DC-4D8E-A4DE-7250D3A7C710}" name="Lesson ID" dataDxfId="57"/>
-    <tableColumn id="11" xr3:uid="{D13F67C3-A32E-454C-AE4D-C716888F27CB}" name="Attendance ID" dataDxfId="56"/>
-    <tableColumn id="12" xr3:uid="{9B183B96-B338-4F28-AD14-AC6E651B6858}" name="Student ID" dataDxfId="55"/>
-    <tableColumn id="13" xr3:uid="{05AE8549-9E32-42AB-9E0E-0BECB84ADE19}" name="Service ID" dataDxfId="54"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}" name="Lessons" displayName="Lessons" ref="B5:Q6" insertRow="1" totalsRowShown="0" headerRowDxfId="87" dataDxfId="85" headerRowBorderDxfId="86" tableBorderDxfId="84">
+  <autoFilter ref="B5:Q6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
+  <tableColumns count="16">
+    <tableColumn id="1" xr3:uid="{C1CFA75B-DE21-4250-99D5-6D2B34197E9D}" name="Date" dataDxfId="83"/>
+    <tableColumn id="3" xr3:uid="{E13660C3-AD05-4CF3-9631-AE40C9F89101}" name="Student" dataDxfId="82"/>
+    <tableColumn id="4" xr3:uid="{18BEE297-19DF-4B3B-B4FD-CFAE8F7A6949}" name="Service" dataDxfId="81"/>
+    <tableColumn id="18" xr3:uid="{856AA0AD-A9D2-4BC4-B64C-DD339BB060A4}" name="Price" dataDxfId="2"/>
+    <tableColumn id="19" xr3:uid="{F88A226A-165B-497E-A103-652D51B5F335}" name="Paid" dataDxfId="1"/>
+    <tableColumn id="20" xr3:uid="{F2CC646E-5F4F-4968-901D-FB64DDD94A6C}" name="Notes" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{6C9740E9-87C2-4CC6-9AAD-1D8340BBB1E2}" name="Price / hour" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{6CA1B731-8C2F-4DA6-B472-EE33DF6113CD}" name="Duration (min)" dataDxfId="80"/>
+    <tableColumn id="8" xr3:uid="{7A134DA8-4763-4978-90B3-711AAD8B520E}" name="Price per student" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{7DCD903B-2C97-4AD2-B1F7-E4B6242A2CC8}" name="Online" dataDxfId="79"/>
+    <tableColumn id="14" xr3:uid="{E380BC68-97E8-4AEA-AEA7-229CB9BBE907}" name="Travel allowance" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{96F08C18-13F5-448F-99C8-A2B2DE97A9B4}" name="Weekend" dataDxfId="78"/>
+    <tableColumn id="15" xr3:uid="{E1686B38-6591-41DA-BC53-FA0A75D72633}" name="Weekend Fee" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{08B3198D-C1DC-4D8E-A4DE-7250D3A7C710}" name="Lesson ID" dataDxfId="77"/>
+    <tableColumn id="11" xr3:uid="{D13F67C3-A32E-454C-AE4D-C716888F27CB}" name="Attendance ID" dataDxfId="76"/>
+    <tableColumn id="12" xr3:uid="{9B183B96-B338-4F28-AD14-AC6E651B6858}" name="Student ID" dataDxfId="75"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C992FC1D-929F-4FCC-8034-BD1DE7AB4724}" name="Invoices" displayName="Invoices" ref="B5:J6" insertRow="1" totalsRowShown="0" headerRowDxfId="82" dataDxfId="80" headerRowBorderDxfId="81" tableBorderDxfId="79">
-  <autoFilter ref="B5:J6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{C69805C5-2DE6-4F5E-8595-BD91192122FB}" name="ID" dataDxfId="78"/>
-    <tableColumn id="2" xr3:uid="{31887EF0-F959-496C-8E82-BFC9313A5BD4}" name="Name" dataDxfId="77"/>
-    <tableColumn id="3" xr3:uid="{BD335C6E-9933-48E1-94D0-D0E510EFF5FB}" name="Created UTC" dataDxfId="76"/>
-    <tableColumn id="4" xr3:uid="{899EB7AE-2A40-41FC-80B1-65CB3A3ADF6E}" name="Payer name" dataDxfId="75"/>
-    <tableColumn id="5" xr3:uid="{3309E227-DE1E-43C5-A6B6-0EC92AFFC66E}" name="Student" dataDxfId="74"/>
-    <tableColumn id="6" xr3:uid="{BB6B6371-F4F3-4ED2-B36B-8B9F19FEC62D}" name="Total" dataDxfId="73"/>
-    <tableColumn id="8" xr3:uid="{BC748279-6F8A-40CD-A73A-4EAEC24A6408}" name="Paid" dataDxfId="72"/>
-    <tableColumn id="12" xr3:uid="{8DFC1E1F-49ED-490A-A022-750D97F2DB5E}" name="Payer ID" dataDxfId="71"/>
-    <tableColumn id="13" xr3:uid="{B0BEC736-D1AC-4A3A-A050-D3DA3F256C81}" name="Line ID" dataDxfId="70"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C992FC1D-929F-4FCC-8034-BD1DE7AB4724}" name="Invoices" displayName="Invoices" ref="B5:I6" insertRow="1" totalsRowShown="0" headerRowDxfId="34" dataDxfId="32" headerRowBorderDxfId="33" tableBorderDxfId="31">
+  <autoFilter ref="B5:I6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{C69805C5-2DE6-4F5E-8595-BD91192122FB}" name="ID" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{31887EF0-F959-496C-8E82-BFC9313A5BD4}" name="Name" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{BD335C6E-9933-48E1-94D0-D0E510EFF5FB}" name="Created UTC" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{899EB7AE-2A40-41FC-80B1-65CB3A3ADF6E}" name="Payer" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{BB6B6371-F4F3-4ED2-B36B-8B9F19FEC62D}" name="Total" dataDxfId="26"/>
+    <tableColumn id="8" xr3:uid="{BC748279-6F8A-40CD-A73A-4EAEC24A6408}" name="Paid" dataDxfId="25"/>
+    <tableColumn id="12" xr3:uid="{8DFC1E1F-49ED-490A-A022-750D97F2DB5E}" name="Payer ID" dataDxfId="24"/>
+    <tableColumn id="13" xr3:uid="{B0BEC736-D1AC-4A3A-A050-D3DA3F256C81}" name="Line ID" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A2CA2C87-2B1E-47CC-B98B-F6DB30254282}" name="Profiles" displayName="Profiles" ref="B5:K6" insertRow="1" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A2CA2C87-2B1E-47CC-B98B-F6DB30254282}" name="Profiles" displayName="Profiles" ref="B5:K6" insertRow="1" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19">
   <autoFilter ref="B5:K6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{2F7003BC-BC4F-49D1-8191-9B7B77A95DAD}" name="Full name" dataDxfId="9"/>
-    <tableColumn id="17" xr3:uid="{1ED8C0D8-B8BF-4CB8-BF2A-11954C2F7E1C}" name="Zip code" dataDxfId="8"/>
-    <tableColumn id="20" xr3:uid="{7DBD046D-D51C-4C4F-8604-D6DEC2103E43}" name="City" dataDxfId="7"/>
-    <tableColumn id="19" xr3:uid="{7D393146-6466-4F51-87B6-10B7C5614A6A}" name="Phone" dataDxfId="6"/>
-    <tableColumn id="18" xr3:uid="{C771F655-E405-4BB5-AD39-3D5A94E1BBE0}" name="CIF/NIF" dataDxfId="5"/>
-    <tableColumn id="23" xr3:uid="{0F800687-A552-4911-A84F-66F27E40B2E9}" name="Email" dataDxfId="4"/>
-    <tableColumn id="22" xr3:uid="{2B05B060-5CA2-4293-8190-C4310A9D436E}" name="Bank name" dataDxfId="3"/>
-    <tableColumn id="21" xr3:uid="{7D5301B1-5635-4EF9-88C0-B2D2B15286FD}" name="Bank account" dataDxfId="2"/>
-    <tableColumn id="24" xr3:uid="{9790EA57-CF62-4EF2-ACAE-3D1545D8BFD5}" name="IVA" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{FAC1AFDA-6CB4-4B8D-A36E-7D10AC1588CA}" name="Address" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{2F7003BC-BC4F-49D1-8191-9B7B77A95DAD}" name="Full name" dataDxfId="18"/>
+    <tableColumn id="17" xr3:uid="{1ED8C0D8-B8BF-4CB8-BF2A-11954C2F7E1C}" name="Zip code" dataDxfId="17"/>
+    <tableColumn id="20" xr3:uid="{7DBD046D-D51C-4C4F-8604-D6DEC2103E43}" name="City" dataDxfId="16"/>
+    <tableColumn id="19" xr3:uid="{7D393146-6466-4F51-87B6-10B7C5614A6A}" name="Phone" dataDxfId="15"/>
+    <tableColumn id="18" xr3:uid="{C771F655-E405-4BB5-AD39-3D5A94E1BBE0}" name="CIF/NIF" dataDxfId="14"/>
+    <tableColumn id="23" xr3:uid="{0F800687-A552-4911-A84F-66F27E40B2E9}" name="Email" dataDxfId="13"/>
+    <tableColumn id="22" xr3:uid="{2B05B060-5CA2-4293-8190-C4310A9D436E}" name="Bank name" dataDxfId="12"/>
+    <tableColumn id="21" xr3:uid="{7D5301B1-5635-4EF9-88C0-B2D2B15286FD}" name="Bank account" dataDxfId="11"/>
+    <tableColumn id="24" xr3:uid="{9790EA57-CF62-4EF2-ACAE-3D1545D8BFD5}" name="IVA" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{FAC1AFDA-6CB4-4B8D-A36E-7D10AC1588CA}" name="Address" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2211,7 +2337,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{349C6D3A-2581-4BC1-B198-043D81DE2DED}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="2" customWidth="1"/>
@@ -2221,41 +2347,45 @@
     <col min="5" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="3" spans="1:5" ht="34.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" ht="34.5" x14ac:dyDescent="0.45">
       <c r="B3" s="19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="20"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="5"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="5"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
-      <c r="D6" s="14"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D6" s="8"/>
+      <c r="E6" s="14"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
     </row>
@@ -2294,7 +2424,7 @@
     </row>
     <row r="3" spans="1:9" ht="34.5" x14ac:dyDescent="0.45">
       <c r="B3" s="19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -2314,25 +2444,25 @@
     <row r="5" spans="1:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="D5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>32</v>
-      </c>
       <c r="H5" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I5" s="5"/>
     </row>
@@ -2371,7 +2501,7 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="13" style="2" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" style="2" customWidth="1"/>
     <col min="3" max="3" width="26.140625" style="2" customWidth="1"/>
     <col min="4" max="4" width="31.28515625" style="2" customWidth="1"/>
     <col min="5" max="5" width="23.7109375" style="2" customWidth="1"/>
@@ -2388,7 +2518,7 @@
     </row>
     <row r="3" spans="1:7" ht="34.5" x14ac:dyDescent="0.45">
       <c r="B3" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -2405,19 +2535,19 @@
     <row r="5" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="D5" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5" s="5"/>
     </row>
@@ -2448,7 +2578,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D59E97CD-50F3-44EA-A57D-8B54153DA60F}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="2" customWidth="1"/>
@@ -2459,10 +2589,11 @@
     <col min="8" max="8" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.85546875" style="2" customWidth="1"/>
     <col min="10" max="10" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="2"/>
+    <col min="11" max="11" width="18.140625" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -2470,9 +2601,9 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
-    <row r="3" spans="1:11" ht="34.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" ht="34.5" x14ac:dyDescent="0.45">
       <c r="B3" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -2480,7 +2611,7 @@
       <c r="F3" s="20"/>
       <c r="G3" s="20"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -2491,13 +2622,13 @@
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>4</v>
@@ -2506,23 +2637,26 @@
         <v>5</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="15" t="s">
-        <v>17</v>
+      <c r="H5" s="6" t="s">
+        <v>44</v>
       </c>
       <c r="I5" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="5"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K5" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="L5" s="5"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2530,11 +2664,12 @@
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
-      <c r="H6" s="14"/>
+      <c r="H6" s="8"/>
       <c r="I6" s="14"/>
-      <c r="J6" s="7"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J6" s="14"/>
+      <c r="K6" s="7"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -2555,7 +2690,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B8EF7-62DE-4FCD-B8E3-460BB4D2C6F0}">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="2" customWidth="1"/>
@@ -2564,18 +2699,20 @@
     <col min="4" max="4" width="31.28515625" style="2" customWidth="1"/>
     <col min="5" max="5" width="23.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="19" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" style="2" customWidth="1"/>
     <col min="8" max="8" width="16.140625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="21.28515625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="2"/>
+    <col min="9" max="9" width="15.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="12.85546875" style="2" customWidth="1"/>
     <col min="11" max="11" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="2"/>
+    <col min="15" max="15" width="9.140625" style="2"/>
+    <col min="16" max="16" width="14.140625" style="2" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -2586,7 +2723,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="3" spans="1:14" ht="34.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:18" ht="34.5" x14ac:dyDescent="0.45">
       <c r="B3" s="19" t="s">
         <v>0</v>
       </c>
@@ -2596,7 +2733,7 @@
       <c r="F3" s="20"/>
       <c r="G3" s="21"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -2611,7 +2748,7 @@
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
     </row>
-    <row r="5" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="6" t="s">
         <v>1</v>
@@ -2623,50 +2760,66 @@
         <v>4</v>
       </c>
       <c r="E5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="J5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="K5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="K5" s="15" t="s">
+      <c r="L5" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="N5" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="O5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="P5" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="Q5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="N5" s="5"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="R5" s="5"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="9"/>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -2690,22 +2843,22 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BEF98F2-4AC5-4AA1-85C9-545C3E11603A}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="13" style="2" customWidth="1"/>
     <col min="3" max="3" width="26.140625" style="2" customWidth="1"/>
     <col min="4" max="4" width="31.28515625" style="2" customWidth="1"/>
-    <col min="5" max="6" width="23.7109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="19" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="2"/>
+    <col min="5" max="5" width="23.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="19" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4"/>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -2713,56 +2866,51 @@
       <c r="E1" s="16"/>
       <c r="F1" s="16"/>
       <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="5"/>
-    </row>
-    <row r="3" spans="1:11" ht="34.5" x14ac:dyDescent="0.45">
+      <c r="H1" s="5"/>
+    </row>
+    <row r="3" spans="1:10" ht="34.5" x14ac:dyDescent="0.45">
       <c r="B3" s="19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
       <c r="E3" s="20"/>
       <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-    </row>
-    <row r="5" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:10" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>42</v>
       </c>
       <c r="I5" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="K5" s="5"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J5" s="5"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2772,20 +2920,18 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B3:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -2819,7 +2965,7 @@
     </row>
     <row r="3" spans="1:12" ht="34.5" x14ac:dyDescent="0.45">
       <c r="B3" s="19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -2846,34 +2992,34 @@
     <row r="5" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="I5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="J5" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="J5" s="6" t="s">
-        <v>42</v>
-      </c>
       <c r="K5" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L5" s="5"/>
     </row>

--- a/Apolo/Assets/Excel/Template.xlsx
+++ b/Apolo/Assets/Excel/Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aruiz\source\repos\alexruizdev\Apolo\Apolo\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C3D36C-BF27-4BF0-B46E-5AD1FE48286B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D8F3251-7064-40EF-BF90-3010A5B39B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="19440" windowHeight="14880" activeTab="6" xr2:uid="{AC1E564E-6DB8-4849-BF2A-83F157C7F386}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="19440" windowHeight="14880" activeTab="5" xr2:uid="{AC1E564E-6DB8-4849-BF2A-83F157C7F386}"/>
   </bookViews>
   <sheets>
     <sheet name="Services" sheetId="8" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Students" sheetId="4" r:id="rId3"/>
     <sheet name="Specifications" sheetId="5" r:id="rId4"/>
     <sheet name="Lessons" sheetId="1" r:id="rId5"/>
-    <sheet name="Invoices" sheetId="3" r:id="rId6"/>
+    <sheet name="Bills" sheetId="3" r:id="rId6"/>
     <sheet name="Profiles" sheetId="9" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="52">
   <si>
     <t>Lessons</t>
   </si>
@@ -71,9 +71,6 @@
     <t>Online</t>
   </si>
   <si>
-    <t>Price per student</t>
-  </si>
-  <si>
     <t>Paid</t>
   </si>
   <si>
@@ -89,9 +86,6 @@
     <t>Student ID</t>
   </si>
   <si>
-    <t>Attendance ID</t>
-  </si>
-  <si>
     <t>Lesson ID</t>
   </si>
   <si>
@@ -176,9 +170,6 @@
     <t>Payer ID</t>
   </si>
   <si>
-    <t>Line ID</t>
-  </si>
-  <si>
     <t>Weekend</t>
   </si>
   <si>
@@ -195,6 +186,21 @@
   </si>
   <si>
     <t>Payer</t>
+  </si>
+  <si>
+    <t>Final Price</t>
+  </si>
+  <si>
+    <t>Bill</t>
+  </si>
+  <si>
+    <t>Base price</t>
+  </si>
+  <si>
+    <t>Bill ID</t>
+  </si>
+  <si>
+    <t>Type</t>
   </si>
 </sst>
 </file>
@@ -238,7 +244,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -263,8 +269,14 @@
         <bgColor theme="6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor theme="6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -450,12 +462,29 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="5" tint="-0.249977111117893"/>
+        <color theme="8" tint="0.59999389629810485"/>
       </left>
-      <right/>
-      <top/>
+      <right style="thin">
+        <color theme="8" tint="0.59999389629810485"/>
+      </right>
+      <top style="thin">
+        <color theme="8" tint="0.59999389629810485"/>
+      </top>
       <bottom style="thin">
-        <color theme="5" tint="-0.249977111117893"/>
+        <color theme="8" tint="0.59999389629810485"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -463,7 +492,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -494,9 +523,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -506,6 +532,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -532,305 +564,76 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
         <name val="Century Gothic"/>
         <family val="2"/>
         <scheme val="none"/>
@@ -874,9 +677,311 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
+      <border>
+        <bottom style="thin">
+          <color theme="5" tint="-0.249977111117893"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="5" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="5" tint="-0.249977111117893"/>
+        </left>
+        <right style="thin">
+          <color theme="5" tint="-0.249977111117893"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="3" tint="0.249977111117893"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
       <border outline="0">
         <bottom style="thin">
-          <color rgb="FF215C98"/>
+          <color theme="3" tint="0.249977111117893"/>
         </bottom>
       </border>
     </dxf>
@@ -897,7 +1002,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor theme="6"/>
@@ -931,176 +1035,6 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FF215C98"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFFFFFFF"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color theme="5" tint="-0.249977111117893"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="6"/>
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="5" tint="-0.249977111117893"/>
-        </left>
-        <right style="thin">
-          <color theme="5" tint="-0.249977111117893"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -1153,6 +1087,24 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1631,6 +1583,24 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1719,114 +1689,180 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <border outline="0">
         <top style="thin">
-          <color theme="3" tint="0.249977111117893"/>
+          <color rgb="FF215C98"/>
         </top>
         <bottom style="thin">
-          <color theme="0"/>
+          <color rgb="FFFFFFFF"/>
         </bottom>
       </border>
     </dxf>
@@ -1841,11 +1877,12 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <border outline="0">
         <bottom style="thin">
-          <color theme="3" tint="0.249977111117893"/>
+          <color rgb="FF215C98"/>
         </bottom>
       </border>
     </dxf>
@@ -1866,6 +1903,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor theme="6"/>
@@ -1898,123 +1936,123 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C0795F78-0156-4685-AF9B-C080EB165C86}" name="Services" displayName="Services" ref="B5:E6" insertRow="1" totalsRowShown="0" headerRowDxfId="74" dataDxfId="72" headerRowBorderDxfId="73" tableBorderDxfId="71">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C0795F78-0156-4685-AF9B-C080EB165C86}" name="Services" displayName="Services" ref="B5:E6" insertRow="1" totalsRowShown="0" headerRowDxfId="73" dataDxfId="71" headerRowBorderDxfId="72" tableBorderDxfId="70">
   <autoFilter ref="B5:E6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{0421A27A-273F-4193-83E8-232DCB727B04}" name="Name" dataDxfId="70"/>
-    <tableColumn id="3" xr3:uid="{F070E4D6-2A8B-4929-BF04-8530F193BF70}" name="Price" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{322E168C-94B6-4464-82B7-AE5BD1C86BBE}" name="Price / h" dataDxfId="69"/>
-    <tableColumn id="10" xr3:uid="{699229C5-F45C-42AE-B09B-A008CEFA4B73}" name="ID" dataDxfId="68"/>
+    <tableColumn id="1" xr3:uid="{0421A27A-273F-4193-83E8-232DCB727B04}" name="Name" dataDxfId="69"/>
+    <tableColumn id="3" xr3:uid="{F070E4D6-2A8B-4929-BF04-8530F193BF70}" name="Price" dataDxfId="68"/>
+    <tableColumn id="2" xr3:uid="{322E168C-94B6-4464-82B7-AE5BD1C86BBE}" name="Price / h" dataDxfId="67"/>
+    <tableColumn id="10" xr3:uid="{699229C5-F45C-42AE-B09B-A008CEFA4B73}" name="ID" dataDxfId="66"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0A79F4B1-F900-45BC-9D44-285E808E7870}" name="Payers" displayName="Payers" ref="B5:H6" insertRow="1" totalsRowShown="0" headerRowDxfId="67" dataDxfId="65" headerRowBorderDxfId="66" tableBorderDxfId="64">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0A79F4B1-F900-45BC-9D44-285E808E7870}" name="Payers" displayName="Payers" ref="B5:H6" insertRow="1" totalsRowShown="0" headerRowDxfId="65" dataDxfId="63" headerRowBorderDxfId="64" tableBorderDxfId="62">
   <autoFilter ref="B5:H6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{5BA77401-135F-49A0-9018-51E3A0234CED}" name="First name" dataDxfId="63"/>
-    <tableColumn id="2" xr3:uid="{EDB180AC-1296-443F-B84C-4D4EE4AE073B}" name="Last name" dataDxfId="62"/>
-    <tableColumn id="3" xr3:uid="{DCE1ACAA-6DAD-4705-81EB-7DFA2DF001BC}" name="Address" dataDxfId="61"/>
-    <tableColumn id="14" xr3:uid="{5B929BF7-C179-40AD-A842-4DFB12038777}" name="Zip code" dataDxfId="60"/>
-    <tableColumn id="15" xr3:uid="{6D6E1C47-E3A4-4383-BEC9-B9EAA078358A}" name="City" dataDxfId="59"/>
-    <tableColumn id="4" xr3:uid="{932DDB97-98FA-4056-8148-3C1EBD8A6957}" name="NIF/CIF" dataDxfId="58"/>
-    <tableColumn id="10" xr3:uid="{E234FAE6-CB9B-4EA0-B055-27B95F566BDE}" name="ID" dataDxfId="57"/>
+    <tableColumn id="1" xr3:uid="{5BA77401-135F-49A0-9018-51E3A0234CED}" name="First name" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{EDB180AC-1296-443F-B84C-4D4EE4AE073B}" name="Last name" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{DCE1ACAA-6DAD-4705-81EB-7DFA2DF001BC}" name="Address" dataDxfId="59"/>
+    <tableColumn id="14" xr3:uid="{5B929BF7-C179-40AD-A842-4DFB12038777}" name="Zip code" dataDxfId="58"/>
+    <tableColumn id="15" xr3:uid="{6D6E1C47-E3A4-4383-BEC9-B9EAA078358A}" name="City" dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{932DDB97-98FA-4056-8148-3C1EBD8A6957}" name="NIF/CIF" dataDxfId="56"/>
+    <tableColumn id="10" xr3:uid="{E234FAE6-CB9B-4EA0-B055-27B95F566BDE}" name="ID" dataDxfId="55"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{921EB506-3A8A-4A0B-B4FB-962E1B230FC8}" name="Students" displayName="Students" ref="B5:F6" insertRow="1" totalsRowShown="0" headerRowDxfId="56" dataDxfId="54" headerRowBorderDxfId="55" tableBorderDxfId="53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{921EB506-3A8A-4A0B-B4FB-962E1B230FC8}" name="Students" displayName="Students" ref="B5:F6" insertRow="1" totalsRowShown="0" headerRowDxfId="54" dataDxfId="52" headerRowBorderDxfId="53" tableBorderDxfId="51">
   <autoFilter ref="B5:F6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{D3B37E7D-9062-40D6-B2B2-0A50D2AF30D8}" name="First name" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{DA765E80-CB03-496C-AB85-04C12F7F6EA1}" name="Last name" dataDxfId="51"/>
-    <tableColumn id="14" xr3:uid="{59DCAFC2-89B1-4CB1-9CF4-2945D31AD0A7}" name="Payer name" dataDxfId="50"/>
-    <tableColumn id="10" xr3:uid="{1186A2E8-3B8B-4232-BAAC-F12E28103DE4}" name="Id" dataDxfId="49"/>
-    <tableColumn id="11" xr3:uid="{2C87B7EC-1CBC-4BF1-BC1B-A80BEE6DF561}" name="PayerId" dataDxfId="48"/>
+    <tableColumn id="2" xr3:uid="{D3B37E7D-9062-40D6-B2B2-0A50D2AF30D8}" name="First name" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{DA765E80-CB03-496C-AB85-04C12F7F6EA1}" name="Last name" dataDxfId="49"/>
+    <tableColumn id="14" xr3:uid="{59DCAFC2-89B1-4CB1-9CF4-2945D31AD0A7}" name="Payer name" dataDxfId="48"/>
+    <tableColumn id="10" xr3:uid="{1186A2E8-3B8B-4232-BAAC-F12E28103DE4}" name="Id" dataDxfId="47"/>
+    <tableColumn id="11" xr3:uid="{2C87B7EC-1CBC-4BF1-BC1B-A80BEE6DF561}" name="PayerId" dataDxfId="46"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AD4BFF54-6050-4EA0-B5EE-4251BB923ED8}" name="Specifications" displayName="Specifications" ref="B5:K6" insertRow="1" totalsRowShown="0" headerRowDxfId="47" dataDxfId="45" headerRowBorderDxfId="46" tableBorderDxfId="44">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AD4BFF54-6050-4EA0-B5EE-4251BB923ED8}" name="Specifications" displayName="Specifications" ref="B5:K6" insertRow="1" totalsRowShown="0" headerRowDxfId="45" dataDxfId="43" headerRowBorderDxfId="44" tableBorderDxfId="42">
   <autoFilter ref="B5:K6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{A984BEB5-CD0A-4CBC-8261-5202F875C894}" name="Name" dataDxfId="43"/>
-    <tableColumn id="2" xr3:uid="{E5D86B37-BC1B-421B-8F67-1924F653B36B}" name="Student name" dataDxfId="42"/>
-    <tableColumn id="3" xr3:uid="{4F31CB14-2A08-4670-A72E-704E0461B7C0}" name="Service" dataDxfId="41"/>
-    <tableColumn id="14" xr3:uid="{2046F612-0B54-4B4A-8FFD-EC5D6AB309E9}" name="Duration" dataDxfId="40"/>
-    <tableColumn id="15" xr3:uid="{3B56031F-69EE-48E1-914B-517D98BD2AF6}" name="Price" dataDxfId="39"/>
-    <tableColumn id="5" xr3:uid="{4CB3842E-EB1D-45CA-9308-72C92977B251}" name="Online" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{E7ED6501-C9FE-4D56-95A1-F6238FF1D18F}" name="Weekend" dataDxfId="38"/>
-    <tableColumn id="10" xr3:uid="{AC948A85-76D1-41F8-8643-7143CFC6B853}" name="ID" dataDxfId="37"/>
-    <tableColumn id="16" xr3:uid="{97831813-DA71-41F9-9C8D-B5BDF0ABEBAF}" name="Student ID" dataDxfId="36"/>
-    <tableColumn id="11" xr3:uid="{CF31A15E-2BAA-48FB-B0FE-4AE64ECEA47C}" name="Service ID" dataDxfId="35"/>
+    <tableColumn id="1" xr3:uid="{A984BEB5-CD0A-4CBC-8261-5202F875C894}" name="Name" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{E5D86B37-BC1B-421B-8F67-1924F653B36B}" name="Student name" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{4F31CB14-2A08-4670-A72E-704E0461B7C0}" name="Service" dataDxfId="39"/>
+    <tableColumn id="14" xr3:uid="{2046F612-0B54-4B4A-8FFD-EC5D6AB309E9}" name="Duration" dataDxfId="38"/>
+    <tableColumn id="15" xr3:uid="{3B56031F-69EE-48E1-914B-517D98BD2AF6}" name="Price" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{4CB3842E-EB1D-45CA-9308-72C92977B251}" name="Online" dataDxfId="36"/>
+    <tableColumn id="4" xr3:uid="{E7ED6501-C9FE-4D56-95A1-F6238FF1D18F}" name="Weekend" dataDxfId="35"/>
+    <tableColumn id="10" xr3:uid="{AC948A85-76D1-41F8-8643-7143CFC6B853}" name="ID" dataDxfId="34"/>
+    <tableColumn id="16" xr3:uid="{97831813-DA71-41F9-9C8D-B5BDF0ABEBAF}" name="Student ID" dataDxfId="33"/>
+    <tableColumn id="11" xr3:uid="{CF31A15E-2BAA-48FB-B0FE-4AE64ECEA47C}" name="Service ID" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}" name="Lessons" displayName="Lessons" ref="B5:Q6" insertRow="1" totalsRowShown="0" headerRowDxfId="87" dataDxfId="85" headerRowBorderDxfId="86" tableBorderDxfId="84">
-  <autoFilter ref="B5:Q6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
-  <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{C1CFA75B-DE21-4250-99D5-6D2B34197E9D}" name="Date" dataDxfId="83"/>
-    <tableColumn id="3" xr3:uid="{E13660C3-AD05-4CF3-9631-AE40C9F89101}" name="Student" dataDxfId="82"/>
-    <tableColumn id="4" xr3:uid="{18BEE297-19DF-4B3B-B4FD-CFAE8F7A6949}" name="Service" dataDxfId="81"/>
-    <tableColumn id="18" xr3:uid="{856AA0AD-A9D2-4BC4-B64C-DD339BB060A4}" name="Price" dataDxfId="2"/>
-    <tableColumn id="19" xr3:uid="{F88A226A-165B-497E-A103-652D51B5F335}" name="Paid" dataDxfId="1"/>
-    <tableColumn id="20" xr3:uid="{F2CC646E-5F4F-4968-901D-FB64DDD94A6C}" name="Notes" dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{6C9740E9-87C2-4CC6-9AAD-1D8340BBB1E2}" name="Price / hour" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{6CA1B731-8C2F-4DA6-B472-EE33DF6113CD}" name="Duration (min)" dataDxfId="80"/>
-    <tableColumn id="8" xr3:uid="{7A134DA8-4763-4978-90B3-711AAD8B520E}" name="Price per student" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{7DCD903B-2C97-4AD2-B1F7-E4B6242A2CC8}" name="Online" dataDxfId="79"/>
-    <tableColumn id="14" xr3:uid="{E380BC68-97E8-4AEA-AEA7-229CB9BBE907}" name="Travel allowance" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{96F08C18-13F5-448F-99C8-A2B2DE97A9B4}" name="Weekend" dataDxfId="78"/>
-    <tableColumn id="15" xr3:uid="{E1686B38-6591-41DA-BC53-FA0A75D72633}" name="Weekend Fee" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{08B3198D-C1DC-4D8E-A4DE-7250D3A7C710}" name="Lesson ID" dataDxfId="77"/>
-    <tableColumn id="11" xr3:uid="{D13F67C3-A32E-454C-AE4D-C716888F27CB}" name="Attendance ID" dataDxfId="76"/>
-    <tableColumn id="12" xr3:uid="{9B183B96-B338-4F28-AD14-AC6E651B6858}" name="Student ID" dataDxfId="75"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}" name="Lessons" displayName="Lessons" ref="B5:R6" insertRow="1" totalsRowShown="0" headerRowDxfId="31" dataDxfId="29" headerRowBorderDxfId="30" tableBorderDxfId="28">
+  <autoFilter ref="B5:R6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
+  <tableColumns count="17">
+    <tableColumn id="1" xr3:uid="{C1CFA75B-DE21-4250-99D5-6D2B34197E9D}" name="Date" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{E13660C3-AD05-4CF3-9631-AE40C9F89101}" name="Service" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{18BEE297-19DF-4B3B-B4FD-CFAE8F7A6949}" name="Student" dataDxfId="25"/>
+    <tableColumn id="18" xr3:uid="{856AA0AD-A9D2-4BC4-B64C-DD339BB060A4}" name="Final Price" dataDxfId="24"/>
+    <tableColumn id="19" xr3:uid="{F88A226A-165B-497E-A103-652D51B5F335}" name="Paid" dataDxfId="23"/>
+    <tableColumn id="20" xr3:uid="{F2CC646E-5F4F-4968-901D-FB64DDD94A6C}" name="Notes" dataDxfId="22"/>
+    <tableColumn id="9" xr3:uid="{8F080EB1-2903-456C-965B-2C7056063FA0}" name="Bill" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{6C9740E9-87C2-4CC6-9AAD-1D8340BBB1E2}" name="Price / hour" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{6CA1B731-8C2F-4DA6-B472-EE33DF6113CD}" name="Duration (min)" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{7A134DA8-4763-4978-90B3-711AAD8B520E}" name="Base price" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{7DCD903B-2C97-4AD2-B1F7-E4B6242A2CC8}" name="Online" dataDxfId="18"/>
+    <tableColumn id="14" xr3:uid="{E380BC68-97E8-4AEA-AEA7-229CB9BBE907}" name="Travel allowance" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{96F08C18-13F5-448F-99C8-A2B2DE97A9B4}" name="Weekend" dataDxfId="16"/>
+    <tableColumn id="15" xr3:uid="{E1686B38-6591-41DA-BC53-FA0A75D72633}" name="Weekend Fee" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{08B3198D-C1DC-4D8E-A4DE-7250D3A7C710}" name="Lesson ID" dataDxfId="14"/>
+    <tableColumn id="11" xr3:uid="{D13F67C3-A32E-454C-AE4D-C716888F27CB}" name="Student ID" dataDxfId="13"/>
+    <tableColumn id="12" xr3:uid="{9B183B96-B338-4F28-AD14-AC6E651B6858}" name="Bill ID" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C992FC1D-929F-4FCC-8034-BD1DE7AB4724}" name="Invoices" displayName="Invoices" ref="B5:I6" insertRow="1" totalsRowShown="0" headerRowDxfId="34" dataDxfId="32" headerRowBorderDxfId="33" tableBorderDxfId="31">
-  <autoFilter ref="B5:I6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C69805C5-2DE6-4F5E-8595-BD91192122FB}" name="ID" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{31887EF0-F959-496C-8E82-BFC9313A5BD4}" name="Name" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{BD335C6E-9933-48E1-94D0-D0E510EFF5FB}" name="Created UTC" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{899EB7AE-2A40-41FC-80B1-65CB3A3ADF6E}" name="Payer" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{BB6B6371-F4F3-4ED2-B36B-8B9F19FEC62D}" name="Total" dataDxfId="26"/>
-    <tableColumn id="8" xr3:uid="{BC748279-6F8A-40CD-A73A-4EAEC24A6408}" name="Paid" dataDxfId="25"/>
-    <tableColumn id="12" xr3:uid="{8DFC1E1F-49ED-490A-A022-750D97F2DB5E}" name="Payer ID" dataDxfId="24"/>
-    <tableColumn id="13" xr3:uid="{B0BEC736-D1AC-4A3A-A050-D3DA3F256C81}" name="Line ID" dataDxfId="23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C992FC1D-929F-4FCC-8034-BD1DE7AB4724}" name="Invoices" displayName="Invoices" ref="B5:H6" insertRow="1" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8">
+  <autoFilter ref="B5:H6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{C69805C5-2DE6-4F5E-8595-BD91192122FB}" name="Name" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{31887EF0-F959-496C-8E82-BFC9313A5BD4}" name="Type" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{BD335C6E-9933-48E1-94D0-D0E510EFF5FB}" name="Created UTC" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{899EB7AE-2A40-41FC-80B1-65CB3A3ADF6E}" name="Payer" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{BB6B6371-F4F3-4ED2-B36B-8B9F19FEC62D}" name="Total" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{8DFC1E1F-49ED-490A-A022-750D97F2DB5E}" name="Payer ID" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{B0BEC736-D1AC-4A3A-A050-D3DA3F256C81}" name="ID" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A2CA2C87-2B1E-47CC-B98B-F6DB30254282}" name="Profiles" displayName="Profiles" ref="B5:K6" insertRow="1" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A2CA2C87-2B1E-47CC-B98B-F6DB30254282}" name="Profiles" displayName="Profiles" ref="B5:K6" insertRow="1" totalsRowShown="0" headerRowDxfId="87" dataDxfId="85" headerRowBorderDxfId="86" tableBorderDxfId="84">
   <autoFilter ref="B5:K6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{2F7003BC-BC4F-49D1-8191-9B7B77A95DAD}" name="Full name" dataDxfId="18"/>
-    <tableColumn id="17" xr3:uid="{1ED8C0D8-B8BF-4CB8-BF2A-11954C2F7E1C}" name="Zip code" dataDxfId="17"/>
-    <tableColumn id="20" xr3:uid="{7DBD046D-D51C-4C4F-8604-D6DEC2103E43}" name="City" dataDxfId="16"/>
-    <tableColumn id="19" xr3:uid="{7D393146-6466-4F51-87B6-10B7C5614A6A}" name="Phone" dataDxfId="15"/>
-    <tableColumn id="18" xr3:uid="{C771F655-E405-4BB5-AD39-3D5A94E1BBE0}" name="CIF/NIF" dataDxfId="14"/>
-    <tableColumn id="23" xr3:uid="{0F800687-A552-4911-A84F-66F27E40B2E9}" name="Email" dataDxfId="13"/>
-    <tableColumn id="22" xr3:uid="{2B05B060-5CA2-4293-8190-C4310A9D436E}" name="Bank name" dataDxfId="12"/>
-    <tableColumn id="21" xr3:uid="{7D5301B1-5635-4EF9-88C0-B2D2B15286FD}" name="Bank account" dataDxfId="11"/>
-    <tableColumn id="24" xr3:uid="{9790EA57-CF62-4EF2-ACAE-3D1545D8BFD5}" name="IVA" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{FAC1AFDA-6CB4-4B8D-A36E-7D10AC1588CA}" name="Address" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{2F7003BC-BC4F-49D1-8191-9B7B77A95DAD}" name="Full name" dataDxfId="83"/>
+    <tableColumn id="17" xr3:uid="{1ED8C0D8-B8BF-4CB8-BF2A-11954C2F7E1C}" name="Zip code" dataDxfId="82"/>
+    <tableColumn id="20" xr3:uid="{7DBD046D-D51C-4C4F-8604-D6DEC2103E43}" name="City" dataDxfId="81"/>
+    <tableColumn id="19" xr3:uid="{7D393146-6466-4F51-87B6-10B7C5614A6A}" name="Phone" dataDxfId="80"/>
+    <tableColumn id="18" xr3:uid="{C771F655-E405-4BB5-AD39-3D5A94E1BBE0}" name="CIF/NIF" dataDxfId="79"/>
+    <tableColumn id="23" xr3:uid="{0F800687-A552-4911-A84F-66F27E40B2E9}" name="Email" dataDxfId="78"/>
+    <tableColumn id="22" xr3:uid="{2B05B060-5CA2-4293-8190-C4310A9D436E}" name="Bank name" dataDxfId="77"/>
+    <tableColumn id="21" xr3:uid="{7D5301B1-5635-4EF9-88C0-B2D2B15286FD}" name="Bank account" dataDxfId="76"/>
+    <tableColumn id="24" xr3:uid="{9790EA57-CF62-4EF2-ACAE-3D1545D8BFD5}" name="IVA" dataDxfId="75"/>
+    <tableColumn id="2" xr3:uid="{FAC1AFDA-6CB4-4B8D-A36E-7D10AC1588CA}" name="Address" dataDxfId="74"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2352,10 +2390,10 @@
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:6" ht="34.5" x14ac:dyDescent="0.45">
-      <c r="B3" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="20"/>
+      <c r="B3" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="19"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
@@ -2368,13 +2406,13 @@
         <v>2</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F5" s="5"/>
     </row>
@@ -2423,14 +2461,14 @@
       <c r="G1" s="1"/>
     </row>
     <row r="3" spans="1:9" ht="34.5" x14ac:dyDescent="0.45">
-      <c r="B3" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
+      <c r="B3" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
@@ -2444,25 +2482,25 @@
     <row r="5" spans="1:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>31</v>
-      </c>
       <c r="H5" s="15" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I5" s="5"/>
     </row>
@@ -2517,12 +2555,12 @@
       <c r="E1" s="1"/>
     </row>
     <row r="3" spans="1:7" ht="34.5" x14ac:dyDescent="0.45">
-      <c r="B3" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
+      <c r="B3" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
@@ -2535,19 +2573,19 @@
     <row r="5" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G5" s="5"/>
     </row>
@@ -2602,14 +2640,14 @@
       <c r="G1" s="1"/>
     </row>
     <row r="3" spans="1:12" ht="34.5" x14ac:dyDescent="0.45">
-      <c r="B3" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
+      <c r="B3" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
@@ -2628,7 +2666,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>4</v>
@@ -2637,22 +2675,22 @@
         <v>5</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>7</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L5" s="5"/>
     </row>
@@ -2690,7 +2728,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B8EF7-62DE-4FCD-B8E3-460BB4D2C6F0}">
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="2" customWidth="1"/>
@@ -2709,10 +2747,12 @@
     <col min="14" max="14" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9.140625" style="2"/>
     <col min="16" max="16" width="14.140625" style="2" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="2"/>
+    <col min="17" max="17" width="9.140625" style="2"/>
+    <col min="18" max="18" width="15.42578125" style="2" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -2723,17 +2763,17 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="3" spans="1:18" ht="34.5" x14ac:dyDescent="0.45">
-      <c r="B3" s="19" t="s">
+    <row r="3" spans="1:19" ht="34.5" x14ac:dyDescent="0.45">
+      <c r="B3" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="21"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="20"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -2747,60 +2787,64 @@
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
-    </row>
-    <row r="5" spans="1:18" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O4" s="3"/>
+    </row>
+    <row r="5" spans="1:19" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>4</v>
-      </c>
       <c r="E5" s="6" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G5" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="J5" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="L5" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="L5" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="M5" s="6" t="s">
+      <c r="M5" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="O5" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="N5" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="O5" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="P5" s="15" t="s">
-        <v>14</v>
+      <c r="P5" s="21" t="s">
+        <v>13</v>
       </c>
       <c r="Q5" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="R5" s="5"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="R5" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="S5" s="5"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="9"/>
       <c r="C6" s="10"/>
@@ -2809,17 +2853,18 @@
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="8"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="12"/>
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
       <c r="N6" s="8"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="7"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="14"/>
       <c r="Q6" s="7"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R6" s="7"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -2869,13 +2914,13 @@
       <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:10" ht="34.5" x14ac:dyDescent="0.45">
-      <c r="B3" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
+      <c r="B3" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H4" s="3"/>
@@ -2885,30 +2930,27 @@
     <row r="5" spans="1:10" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="17" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>9</v>
+        <v>18</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>40</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="J5" s="5"/>
+        <v>14</v>
+      </c>
+      <c r="I5" s="5"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
@@ -2919,7 +2961,6 @@
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" s="7"/>
@@ -2964,18 +3005,18 @@
       <c r="K1" s="1"/>
     </row>
     <row r="3" spans="1:12" ht="34.5" x14ac:dyDescent="0.45">
-      <c r="B3" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
+      <c r="B3" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
@@ -2992,34 +3033,34 @@
     <row r="5" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="I5" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="J5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="I5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>41</v>
-      </c>
       <c r="K5" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L5" s="5"/>
     </row>

--- a/Apolo/Assets/Excel/Template.xlsx
+++ b/Apolo/Assets/Excel/Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aruiz\source\repos\alexruizdev\Apolo\Apolo\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D8F3251-7064-40EF-BF90-3010A5B39B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC223A67-7189-4900-9389-1A63A2845F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="19440" windowHeight="14880" activeTab="5" xr2:uid="{AC1E564E-6DB8-4849-BF2A-83F157C7F386}"/>
   </bookViews>
@@ -523,6 +523,12 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -532,12 +538,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -545,6 +545,19 @@
   <dxfs count="88">
     <dxf>
       <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -560,7 +573,1197 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF215C98"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFFFFFFF"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF215C98"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="3" tint="0.24994659260841701"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="3" tint="0.249977111117893"/>
+        </left>
+        <right style="thin">
+          <color theme="3" tint="0.249977111117893"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="3" tint="0.249977111117893"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="3" tint="0.249977111117893"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="3" tint="0.24994659260841701"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="3" tint="0.249977111117893"/>
+        </left>
+        <right style="thin">
+          <color theme="3" tint="0.249977111117893"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top/>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF215C98"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFFFFFFF"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF215C98"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="3" tint="0.24994659260841701"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="3" tint="0.249977111117893"/>
+        </left>
+        <right style="thin">
+          <color theme="3" tint="0.249977111117893"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF215C98"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFFFFFFF"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF215C98"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="3" tint="0.24994659260841701"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="3" tint="0.249977111117893"/>
+        </left>
+        <right style="thin">
+          <color theme="3" tint="0.249977111117893"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF215C98"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFFFFFFF"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF215C98"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="3" tint="0.24994659260841701"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="3" tint="0.249977111117893"/>
+        </left>
+        <right style="thin">
+          <color theme="3" tint="0.249977111117893"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF215C98"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFFFFFFF"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF215C98"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="3" tint="0.24994659260841701"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="3" tint="0.249977111117893"/>
+        </left>
+        <right style="thin">
+          <color theme="3" tint="0.249977111117893"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -719,1209 +1922,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="3" tint="0.249977111117893"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="3" tint="0.249977111117893"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="6"/>
-          <bgColor theme="3" tint="0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="3" tint="0.249977111117893"/>
-        </left>
-        <right style="thin">
-          <color theme="3" tint="0.249977111117893"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color theme="0"/>
-        </right>
-        <top/>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FF215C98"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFFFFFFF"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF215C98"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="6"/>
-          <bgColor theme="3" tint="0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="3" tint="0.249977111117893"/>
-        </left>
-        <right style="thin">
-          <color theme="3" tint="0.249977111117893"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FF215C98"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFFFFFFF"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF215C98"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="6"/>
-          <bgColor theme="3" tint="0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="3" tint="0.249977111117893"/>
-        </left>
-        <right style="thin">
-          <color theme="3" tint="0.249977111117893"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FF215C98"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFFFFFFF"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF215C98"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="6"/>
-          <bgColor theme="3" tint="0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="3" tint="0.249977111117893"/>
-        </left>
-        <right style="thin">
-          <color theme="3" tint="0.249977111117893"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FF215C98"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFFFFFFF"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF215C98"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="6"/>
-          <bgColor theme="3" tint="0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="3" tint="0.249977111117893"/>
-        </left>
-        <right style="thin">
-          <color theme="3" tint="0.249977111117893"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FF215C98"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFFFFFFF"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF215C98"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="6"/>
-          <bgColor theme="3" tint="0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="3" tint="0.249977111117893"/>
-        </left>
-        <right style="thin">
-          <color theme="3" tint="0.249977111117893"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1936,123 +1936,123 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C0795F78-0156-4685-AF9B-C080EB165C86}" name="Services" displayName="Services" ref="B5:E6" insertRow="1" totalsRowShown="0" headerRowDxfId="73" dataDxfId="71" headerRowBorderDxfId="72" tableBorderDxfId="70">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C0795F78-0156-4685-AF9B-C080EB165C86}" name="Services" displayName="Services" ref="B5:E6" insertRow="1" totalsRowShown="0" headerRowDxfId="76" dataDxfId="74" headerRowBorderDxfId="75" tableBorderDxfId="73">
   <autoFilter ref="B5:E6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{0421A27A-273F-4193-83E8-232DCB727B04}" name="Name" dataDxfId="69"/>
-    <tableColumn id="3" xr3:uid="{F070E4D6-2A8B-4929-BF04-8530F193BF70}" name="Price" dataDxfId="68"/>
-    <tableColumn id="2" xr3:uid="{322E168C-94B6-4464-82B7-AE5BD1C86BBE}" name="Price / h" dataDxfId="67"/>
-    <tableColumn id="10" xr3:uid="{699229C5-F45C-42AE-B09B-A008CEFA4B73}" name="ID" dataDxfId="66"/>
+    <tableColumn id="1" xr3:uid="{0421A27A-273F-4193-83E8-232DCB727B04}" name="Name" dataDxfId="72"/>
+    <tableColumn id="3" xr3:uid="{F070E4D6-2A8B-4929-BF04-8530F193BF70}" name="Price" dataDxfId="71"/>
+    <tableColumn id="2" xr3:uid="{322E168C-94B6-4464-82B7-AE5BD1C86BBE}" name="Price / h" dataDxfId="70"/>
+    <tableColumn id="10" xr3:uid="{699229C5-F45C-42AE-B09B-A008CEFA4B73}" name="ID" dataDxfId="69"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0A79F4B1-F900-45BC-9D44-285E808E7870}" name="Payers" displayName="Payers" ref="B5:H6" insertRow="1" totalsRowShown="0" headerRowDxfId="65" dataDxfId="63" headerRowBorderDxfId="64" tableBorderDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0A79F4B1-F900-45BC-9D44-285E808E7870}" name="Payers" displayName="Payers" ref="B5:H6" insertRow="1" totalsRowShown="0" headerRowDxfId="68" dataDxfId="66" headerRowBorderDxfId="67" tableBorderDxfId="65">
   <autoFilter ref="B5:H6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{5BA77401-135F-49A0-9018-51E3A0234CED}" name="First name" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{EDB180AC-1296-443F-B84C-4D4EE4AE073B}" name="Last name" dataDxfId="60"/>
-    <tableColumn id="3" xr3:uid="{DCE1ACAA-6DAD-4705-81EB-7DFA2DF001BC}" name="Address" dataDxfId="59"/>
-    <tableColumn id="14" xr3:uid="{5B929BF7-C179-40AD-A842-4DFB12038777}" name="Zip code" dataDxfId="58"/>
-    <tableColumn id="15" xr3:uid="{6D6E1C47-E3A4-4383-BEC9-B9EAA078358A}" name="City" dataDxfId="57"/>
-    <tableColumn id="4" xr3:uid="{932DDB97-98FA-4056-8148-3C1EBD8A6957}" name="NIF/CIF" dataDxfId="56"/>
-    <tableColumn id="10" xr3:uid="{E234FAE6-CB9B-4EA0-B055-27B95F566BDE}" name="ID" dataDxfId="55"/>
+    <tableColumn id="1" xr3:uid="{5BA77401-135F-49A0-9018-51E3A0234CED}" name="First name" dataDxfId="64"/>
+    <tableColumn id="2" xr3:uid="{EDB180AC-1296-443F-B84C-4D4EE4AE073B}" name="Last name" dataDxfId="63"/>
+    <tableColumn id="3" xr3:uid="{DCE1ACAA-6DAD-4705-81EB-7DFA2DF001BC}" name="Address" dataDxfId="62"/>
+    <tableColumn id="14" xr3:uid="{5B929BF7-C179-40AD-A842-4DFB12038777}" name="Zip code" dataDxfId="61"/>
+    <tableColumn id="15" xr3:uid="{6D6E1C47-E3A4-4383-BEC9-B9EAA078358A}" name="City" dataDxfId="60"/>
+    <tableColumn id="4" xr3:uid="{932DDB97-98FA-4056-8148-3C1EBD8A6957}" name="NIF/CIF" dataDxfId="59"/>
+    <tableColumn id="10" xr3:uid="{E234FAE6-CB9B-4EA0-B055-27B95F566BDE}" name="ID" dataDxfId="58"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{921EB506-3A8A-4A0B-B4FB-962E1B230FC8}" name="Students" displayName="Students" ref="B5:F6" insertRow="1" totalsRowShown="0" headerRowDxfId="54" dataDxfId="52" headerRowBorderDxfId="53" tableBorderDxfId="51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{921EB506-3A8A-4A0B-B4FB-962E1B230FC8}" name="Students" displayName="Students" ref="B5:F6" insertRow="1" totalsRowShown="0" headerRowDxfId="57" dataDxfId="55" headerRowBorderDxfId="56" tableBorderDxfId="54">
   <autoFilter ref="B5:F6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{D3B37E7D-9062-40D6-B2B2-0A50D2AF30D8}" name="First name" dataDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{DA765E80-CB03-496C-AB85-04C12F7F6EA1}" name="Last name" dataDxfId="49"/>
-    <tableColumn id="14" xr3:uid="{59DCAFC2-89B1-4CB1-9CF4-2945D31AD0A7}" name="Payer name" dataDxfId="48"/>
-    <tableColumn id="10" xr3:uid="{1186A2E8-3B8B-4232-BAAC-F12E28103DE4}" name="Id" dataDxfId="47"/>
-    <tableColumn id="11" xr3:uid="{2C87B7EC-1CBC-4BF1-BC1B-A80BEE6DF561}" name="PayerId" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{D3B37E7D-9062-40D6-B2B2-0A50D2AF30D8}" name="First name" dataDxfId="53"/>
+    <tableColumn id="3" xr3:uid="{DA765E80-CB03-496C-AB85-04C12F7F6EA1}" name="Last name" dataDxfId="52"/>
+    <tableColumn id="14" xr3:uid="{59DCAFC2-89B1-4CB1-9CF4-2945D31AD0A7}" name="Payer name" dataDxfId="51"/>
+    <tableColumn id="10" xr3:uid="{1186A2E8-3B8B-4232-BAAC-F12E28103DE4}" name="Id" dataDxfId="50"/>
+    <tableColumn id="11" xr3:uid="{2C87B7EC-1CBC-4BF1-BC1B-A80BEE6DF561}" name="PayerId" dataDxfId="49"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AD4BFF54-6050-4EA0-B5EE-4251BB923ED8}" name="Specifications" displayName="Specifications" ref="B5:K6" insertRow="1" totalsRowShown="0" headerRowDxfId="45" dataDxfId="43" headerRowBorderDxfId="44" tableBorderDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AD4BFF54-6050-4EA0-B5EE-4251BB923ED8}" name="Specifications" displayName="Specifications" ref="B5:K6" insertRow="1" totalsRowShown="0" headerRowDxfId="48" dataDxfId="46" headerRowBorderDxfId="47" tableBorderDxfId="45">
   <autoFilter ref="B5:K6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{A984BEB5-CD0A-4CBC-8261-5202F875C894}" name="Name" dataDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{E5D86B37-BC1B-421B-8F67-1924F653B36B}" name="Student name" dataDxfId="40"/>
-    <tableColumn id="3" xr3:uid="{4F31CB14-2A08-4670-A72E-704E0461B7C0}" name="Service" dataDxfId="39"/>
-    <tableColumn id="14" xr3:uid="{2046F612-0B54-4B4A-8FFD-EC5D6AB309E9}" name="Duration" dataDxfId="38"/>
-    <tableColumn id="15" xr3:uid="{3B56031F-69EE-48E1-914B-517D98BD2AF6}" name="Price" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{4CB3842E-EB1D-45CA-9308-72C92977B251}" name="Online" dataDxfId="36"/>
-    <tableColumn id="4" xr3:uid="{E7ED6501-C9FE-4D56-95A1-F6238FF1D18F}" name="Weekend" dataDxfId="35"/>
-    <tableColumn id="10" xr3:uid="{AC948A85-76D1-41F8-8643-7143CFC6B853}" name="ID" dataDxfId="34"/>
-    <tableColumn id="16" xr3:uid="{97831813-DA71-41F9-9C8D-B5BDF0ABEBAF}" name="Student ID" dataDxfId="33"/>
-    <tableColumn id="11" xr3:uid="{CF31A15E-2BAA-48FB-B0FE-4AE64ECEA47C}" name="Service ID" dataDxfId="32"/>
+    <tableColumn id="1" xr3:uid="{A984BEB5-CD0A-4CBC-8261-5202F875C894}" name="Name" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{E5D86B37-BC1B-421B-8F67-1924F653B36B}" name="Student name" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{4F31CB14-2A08-4670-A72E-704E0461B7C0}" name="Service" dataDxfId="42"/>
+    <tableColumn id="14" xr3:uid="{2046F612-0B54-4B4A-8FFD-EC5D6AB309E9}" name="Duration" dataDxfId="41"/>
+    <tableColumn id="15" xr3:uid="{3B56031F-69EE-48E1-914B-517D98BD2AF6}" name="Price" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{4CB3842E-EB1D-45CA-9308-72C92977B251}" name="Online" dataDxfId="39"/>
+    <tableColumn id="4" xr3:uid="{E7ED6501-C9FE-4D56-95A1-F6238FF1D18F}" name="Weekend" dataDxfId="38"/>
+    <tableColumn id="10" xr3:uid="{AC948A85-76D1-41F8-8643-7143CFC6B853}" name="ID" dataDxfId="37"/>
+    <tableColumn id="16" xr3:uid="{97831813-DA71-41F9-9C8D-B5BDF0ABEBAF}" name="Student ID" dataDxfId="36"/>
+    <tableColumn id="11" xr3:uid="{CF31A15E-2BAA-48FB-B0FE-4AE64ECEA47C}" name="Service ID" dataDxfId="35"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}" name="Lessons" displayName="Lessons" ref="B5:R6" insertRow="1" totalsRowShown="0" headerRowDxfId="31" dataDxfId="29" headerRowBorderDxfId="30" tableBorderDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}" name="Lessons" displayName="Lessons" ref="B5:R6" insertRow="1" totalsRowShown="0" headerRowDxfId="34" dataDxfId="32" headerRowBorderDxfId="33" tableBorderDxfId="31">
   <autoFilter ref="B5:R6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{C1CFA75B-DE21-4250-99D5-6D2B34197E9D}" name="Date" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{E13660C3-AD05-4CF3-9631-AE40C9F89101}" name="Service" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{18BEE297-19DF-4B3B-B4FD-CFAE8F7A6949}" name="Student" dataDxfId="25"/>
-    <tableColumn id="18" xr3:uid="{856AA0AD-A9D2-4BC4-B64C-DD339BB060A4}" name="Final Price" dataDxfId="24"/>
-    <tableColumn id="19" xr3:uid="{F88A226A-165B-497E-A103-652D51B5F335}" name="Paid" dataDxfId="23"/>
-    <tableColumn id="20" xr3:uid="{F2CC646E-5F4F-4968-901D-FB64DDD94A6C}" name="Notes" dataDxfId="22"/>
-    <tableColumn id="9" xr3:uid="{8F080EB1-2903-456C-965B-2C7056063FA0}" name="Bill" dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{6C9740E9-87C2-4CC6-9AAD-1D8340BBB1E2}" name="Price / hour" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{6CA1B731-8C2F-4DA6-B472-EE33DF6113CD}" name="Duration (min)" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{7A134DA8-4763-4978-90B3-711AAD8B520E}" name="Base price" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{7DCD903B-2C97-4AD2-B1F7-E4B6242A2CC8}" name="Online" dataDxfId="18"/>
-    <tableColumn id="14" xr3:uid="{E380BC68-97E8-4AEA-AEA7-229CB9BBE907}" name="Travel allowance" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{96F08C18-13F5-448F-99C8-A2B2DE97A9B4}" name="Weekend" dataDxfId="16"/>
-    <tableColumn id="15" xr3:uid="{E1686B38-6591-41DA-BC53-FA0A75D72633}" name="Weekend Fee" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{08B3198D-C1DC-4D8E-A4DE-7250D3A7C710}" name="Lesson ID" dataDxfId="14"/>
-    <tableColumn id="11" xr3:uid="{D13F67C3-A32E-454C-AE4D-C716888F27CB}" name="Student ID" dataDxfId="13"/>
-    <tableColumn id="12" xr3:uid="{9B183B96-B338-4F28-AD14-AC6E651B6858}" name="Bill ID" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{C1CFA75B-DE21-4250-99D5-6D2B34197E9D}" name="Date" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{E13660C3-AD05-4CF3-9631-AE40C9F89101}" name="Service" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{18BEE297-19DF-4B3B-B4FD-CFAE8F7A6949}" name="Student" dataDxfId="28"/>
+    <tableColumn id="18" xr3:uid="{856AA0AD-A9D2-4BC4-B64C-DD339BB060A4}" name="Final Price" dataDxfId="27"/>
+    <tableColumn id="19" xr3:uid="{F88A226A-165B-497E-A103-652D51B5F335}" name="Paid" dataDxfId="26"/>
+    <tableColumn id="20" xr3:uid="{F2CC646E-5F4F-4968-901D-FB64DDD94A6C}" name="Notes" dataDxfId="25"/>
+    <tableColumn id="9" xr3:uid="{8F080EB1-2903-456C-965B-2C7056063FA0}" name="Bill" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{6C9740E9-87C2-4CC6-9AAD-1D8340BBB1E2}" name="Price / hour" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{6CA1B731-8C2F-4DA6-B472-EE33DF6113CD}" name="Duration (min)" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{7A134DA8-4763-4978-90B3-711AAD8B520E}" name="Base price" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{7DCD903B-2C97-4AD2-B1F7-E4B6242A2CC8}" name="Online" dataDxfId="20"/>
+    <tableColumn id="14" xr3:uid="{E380BC68-97E8-4AEA-AEA7-229CB9BBE907}" name="Travel allowance" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{96F08C18-13F5-448F-99C8-A2B2DE97A9B4}" name="Weekend" dataDxfId="18"/>
+    <tableColumn id="15" xr3:uid="{E1686B38-6591-41DA-BC53-FA0A75D72633}" name="Weekend Fee" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{08B3198D-C1DC-4D8E-A4DE-7250D3A7C710}" name="Lesson ID" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{D13F67C3-A32E-454C-AE4D-C716888F27CB}" name="Student ID" dataDxfId="15"/>
+    <tableColumn id="12" xr3:uid="{9B183B96-B338-4F28-AD14-AC6E651B6858}" name="Bill ID" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C992FC1D-929F-4FCC-8034-BD1DE7AB4724}" name="Invoices" displayName="Invoices" ref="B5:H6" insertRow="1" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C992FC1D-929F-4FCC-8034-BD1DE7AB4724}" name="Bills" displayName="Bills" ref="B5:H6" insertRow="1" totalsRowShown="0" headerRowDxfId="87" dataDxfId="85" headerRowBorderDxfId="86" tableBorderDxfId="84">
   <autoFilter ref="B5:H6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{C69805C5-2DE6-4F5E-8595-BD91192122FB}" name="Name" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{31887EF0-F959-496C-8E82-BFC9313A5BD4}" name="Type" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{BD335C6E-9933-48E1-94D0-D0E510EFF5FB}" name="Created UTC" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{899EB7AE-2A40-41FC-80B1-65CB3A3ADF6E}" name="Payer" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{BB6B6371-F4F3-4ED2-B36B-8B9F19FEC62D}" name="Total" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{8DFC1E1F-49ED-490A-A022-750D97F2DB5E}" name="Payer ID" dataDxfId="2"/>
-    <tableColumn id="13" xr3:uid="{B0BEC736-D1AC-4A3A-A050-D3DA3F256C81}" name="ID" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{C69805C5-2DE6-4F5E-8595-BD91192122FB}" name="Name" dataDxfId="83"/>
+    <tableColumn id="2" xr3:uid="{31887EF0-F959-496C-8E82-BFC9313A5BD4}" name="Type" dataDxfId="82"/>
+    <tableColumn id="3" xr3:uid="{BD335C6E-9933-48E1-94D0-D0E510EFF5FB}" name="Created UTC" dataDxfId="81"/>
+    <tableColumn id="4" xr3:uid="{899EB7AE-2A40-41FC-80B1-65CB3A3ADF6E}" name="Payer" dataDxfId="80"/>
+    <tableColumn id="6" xr3:uid="{BB6B6371-F4F3-4ED2-B36B-8B9F19FEC62D}" name="Total" dataDxfId="79"/>
+    <tableColumn id="12" xr3:uid="{8DFC1E1F-49ED-490A-A022-750D97F2DB5E}" name="Payer ID" dataDxfId="78"/>
+    <tableColumn id="13" xr3:uid="{B0BEC736-D1AC-4A3A-A050-D3DA3F256C81}" name="ID" dataDxfId="77"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A2CA2C87-2B1E-47CC-B98B-F6DB30254282}" name="Profiles" displayName="Profiles" ref="B5:K6" insertRow="1" totalsRowShown="0" headerRowDxfId="87" dataDxfId="85" headerRowBorderDxfId="86" tableBorderDxfId="84">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A2CA2C87-2B1E-47CC-B98B-F6DB30254282}" name="Profiles" displayName="Profiles" ref="B5:K6" insertRow="1" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10">
   <autoFilter ref="B5:K6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{2F7003BC-BC4F-49D1-8191-9B7B77A95DAD}" name="Full name" dataDxfId="83"/>
-    <tableColumn id="17" xr3:uid="{1ED8C0D8-B8BF-4CB8-BF2A-11954C2F7E1C}" name="Zip code" dataDxfId="82"/>
-    <tableColumn id="20" xr3:uid="{7DBD046D-D51C-4C4F-8604-D6DEC2103E43}" name="City" dataDxfId="81"/>
-    <tableColumn id="19" xr3:uid="{7D393146-6466-4F51-87B6-10B7C5614A6A}" name="Phone" dataDxfId="80"/>
-    <tableColumn id="18" xr3:uid="{C771F655-E405-4BB5-AD39-3D5A94E1BBE0}" name="CIF/NIF" dataDxfId="79"/>
-    <tableColumn id="23" xr3:uid="{0F800687-A552-4911-A84F-66F27E40B2E9}" name="Email" dataDxfId="78"/>
-    <tableColumn id="22" xr3:uid="{2B05B060-5CA2-4293-8190-C4310A9D436E}" name="Bank name" dataDxfId="77"/>
-    <tableColumn id="21" xr3:uid="{7D5301B1-5635-4EF9-88C0-B2D2B15286FD}" name="Bank account" dataDxfId="76"/>
-    <tableColumn id="24" xr3:uid="{9790EA57-CF62-4EF2-ACAE-3D1545D8BFD5}" name="IVA" dataDxfId="75"/>
-    <tableColumn id="2" xr3:uid="{FAC1AFDA-6CB4-4B8D-A36E-7D10AC1588CA}" name="Address" dataDxfId="74"/>
+    <tableColumn id="1" xr3:uid="{2F7003BC-BC4F-49D1-8191-9B7B77A95DAD}" name="Full name" dataDxfId="9"/>
+    <tableColumn id="17" xr3:uid="{1ED8C0D8-B8BF-4CB8-BF2A-11954C2F7E1C}" name="Zip code" dataDxfId="8"/>
+    <tableColumn id="20" xr3:uid="{7DBD046D-D51C-4C4F-8604-D6DEC2103E43}" name="City" dataDxfId="7"/>
+    <tableColumn id="19" xr3:uid="{7D393146-6466-4F51-87B6-10B7C5614A6A}" name="Phone" dataDxfId="6"/>
+    <tableColumn id="18" xr3:uid="{C771F655-E405-4BB5-AD39-3D5A94E1BBE0}" name="CIF/NIF" dataDxfId="5"/>
+    <tableColumn id="23" xr3:uid="{0F800687-A552-4911-A84F-66F27E40B2E9}" name="Email" dataDxfId="4"/>
+    <tableColumn id="22" xr3:uid="{2B05B060-5CA2-4293-8190-C4310A9D436E}" name="Bank name" dataDxfId="3"/>
+    <tableColumn id="21" xr3:uid="{7D5301B1-5635-4EF9-88C0-B2D2B15286FD}" name="Bank account" dataDxfId="2"/>
+    <tableColumn id="24" xr3:uid="{9790EA57-CF62-4EF2-ACAE-3D1545D8BFD5}" name="IVA" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{FAC1AFDA-6CB4-4B8D-A36E-7D10AC1588CA}" name="Address" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2390,10 +2390,10 @@
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:6" ht="34.5" x14ac:dyDescent="0.45">
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="19"/>
+      <c r="C3" s="21"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
@@ -2461,14 +2461,14 @@
       <c r="G1" s="1"/>
     </row>
     <row r="3" spans="1:9" ht="34.5" x14ac:dyDescent="0.45">
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
@@ -2555,12 +2555,12 @@
       <c r="E1" s="1"/>
     </row>
     <row r="3" spans="1:7" ht="34.5" x14ac:dyDescent="0.45">
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
@@ -2640,14 +2640,14 @@
       <c r="G1" s="1"/>
     </row>
     <row r="3" spans="1:12" ht="34.5" x14ac:dyDescent="0.45">
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
@@ -2764,14 +2764,14 @@
       <c r="J1" s="1"/>
     </row>
     <row r="3" spans="1:19" ht="34.5" x14ac:dyDescent="0.45">
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="22"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
@@ -2812,28 +2812,28 @@
       <c r="H5" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="I5" s="22" t="s">
+      <c r="I5" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="J5" s="22" t="s">
+      <c r="J5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="K5" s="22" t="s">
+      <c r="K5" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="L5" s="22" t="s">
+      <c r="L5" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="M5" s="22" t="s">
+      <c r="M5" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="N5" s="22" t="s">
+      <c r="N5" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="O5" s="22" t="s">
+      <c r="O5" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="P5" s="21" t="s">
+      <c r="P5" s="18" t="s">
         <v>13</v>
       </c>
       <c r="Q5" s="15" t="s">
@@ -2914,13 +2914,13 @@
       <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:10" ht="34.5" x14ac:dyDescent="0.45">
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H4" s="3"/>
@@ -3005,18 +3005,18 @@
       <c r="K1" s="1"/>
     </row>
     <row r="3" spans="1:12" ht="34.5" x14ac:dyDescent="0.45">
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>

--- a/Apolo/Assets/Excel/Template.xlsx
+++ b/Apolo/Assets/Excel/Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aruiz\source\repos\alexruizdev\Apolo\Apolo\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC223A67-7189-4900-9389-1A63A2845F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B203FFE-5858-465E-9140-06F42791270F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="19440" windowHeight="14880" activeTab="5" xr2:uid="{AC1E564E-6DB8-4849-BF2A-83F157C7F386}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="55">
   <si>
     <t>Lessons</t>
   </si>
@@ -134,9 +134,6 @@
     <t>City</t>
   </si>
   <si>
-    <t>NIF/CIF</t>
-  </si>
-  <si>
     <t>Services</t>
   </si>
   <si>
@@ -201,6 +198,18 @@
   </si>
   <si>
     <t>Type</t>
+  </si>
+  <si>
+    <t>Tip</t>
+  </si>
+  <si>
+    <t>Usage</t>
+  </si>
+  <si>
+    <t>Sequence</t>
+  </si>
+  <si>
+    <t>Tax Id</t>
   </si>
 </sst>
 </file>
@@ -492,7 +501,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -538,11 +547,67 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="88">
+  <dxfs count="91">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1936,123 +2001,126 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C0795F78-0156-4685-AF9B-C080EB165C86}" name="Services" displayName="Services" ref="B5:E6" insertRow="1" totalsRowShown="0" headerRowDxfId="76" dataDxfId="74" headerRowBorderDxfId="75" tableBorderDxfId="73">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C0795F78-0156-4685-AF9B-C080EB165C86}" name="Services" displayName="Services" ref="B5:E6" insertRow="1" totalsRowShown="0" headerRowDxfId="79" dataDxfId="77" headerRowBorderDxfId="78" tableBorderDxfId="76">
   <autoFilter ref="B5:E6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{0421A27A-273F-4193-83E8-232DCB727B04}" name="Name" dataDxfId="72"/>
-    <tableColumn id="3" xr3:uid="{F070E4D6-2A8B-4929-BF04-8530F193BF70}" name="Price" dataDxfId="71"/>
-    <tableColumn id="2" xr3:uid="{322E168C-94B6-4464-82B7-AE5BD1C86BBE}" name="Price / h" dataDxfId="70"/>
-    <tableColumn id="10" xr3:uid="{699229C5-F45C-42AE-B09B-A008CEFA4B73}" name="ID" dataDxfId="69"/>
+    <tableColumn id="1" xr3:uid="{0421A27A-273F-4193-83E8-232DCB727B04}" name="Name" dataDxfId="75"/>
+    <tableColumn id="3" xr3:uid="{F070E4D6-2A8B-4929-BF04-8530F193BF70}" name="Price" dataDxfId="74"/>
+    <tableColumn id="2" xr3:uid="{322E168C-94B6-4464-82B7-AE5BD1C86BBE}" name="Price / h" dataDxfId="73"/>
+    <tableColumn id="10" xr3:uid="{699229C5-F45C-42AE-B09B-A008CEFA4B73}" name="ID" dataDxfId="72"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0A79F4B1-F900-45BC-9D44-285E808E7870}" name="Payers" displayName="Payers" ref="B5:H6" insertRow="1" totalsRowShown="0" headerRowDxfId="68" dataDxfId="66" headerRowBorderDxfId="67" tableBorderDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0A79F4B1-F900-45BC-9D44-285E808E7870}" name="Payers" displayName="Payers" ref="B5:H6" insertRow="1" totalsRowShown="0" headerRowDxfId="71" dataDxfId="69" headerRowBorderDxfId="70" tableBorderDxfId="68">
   <autoFilter ref="B5:H6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{5BA77401-135F-49A0-9018-51E3A0234CED}" name="First name" dataDxfId="64"/>
-    <tableColumn id="2" xr3:uid="{EDB180AC-1296-443F-B84C-4D4EE4AE073B}" name="Last name" dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{DCE1ACAA-6DAD-4705-81EB-7DFA2DF001BC}" name="Address" dataDxfId="62"/>
-    <tableColumn id="14" xr3:uid="{5B929BF7-C179-40AD-A842-4DFB12038777}" name="Zip code" dataDxfId="61"/>
-    <tableColumn id="15" xr3:uid="{6D6E1C47-E3A4-4383-BEC9-B9EAA078358A}" name="City" dataDxfId="60"/>
-    <tableColumn id="4" xr3:uid="{932DDB97-98FA-4056-8148-3C1EBD8A6957}" name="NIF/CIF" dataDxfId="59"/>
-    <tableColumn id="10" xr3:uid="{E234FAE6-CB9B-4EA0-B055-27B95F566BDE}" name="ID" dataDxfId="58"/>
+    <tableColumn id="1" xr3:uid="{5BA77401-135F-49A0-9018-51E3A0234CED}" name="First name" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{EDB180AC-1296-443F-B84C-4D4EE4AE073B}" name="Last name" dataDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{DCE1ACAA-6DAD-4705-81EB-7DFA2DF001BC}" name="Address" dataDxfId="65"/>
+    <tableColumn id="14" xr3:uid="{5B929BF7-C179-40AD-A842-4DFB12038777}" name="Zip code" dataDxfId="64"/>
+    <tableColumn id="15" xr3:uid="{6D6E1C47-E3A4-4383-BEC9-B9EAA078358A}" name="City" dataDxfId="63"/>
+    <tableColumn id="4" xr3:uid="{932DDB97-98FA-4056-8148-3C1EBD8A6957}" name="Tax Id" dataDxfId="62"/>
+    <tableColumn id="10" xr3:uid="{E234FAE6-CB9B-4EA0-B055-27B95F566BDE}" name="ID" dataDxfId="61"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{921EB506-3A8A-4A0B-B4FB-962E1B230FC8}" name="Students" displayName="Students" ref="B5:F6" insertRow="1" totalsRowShown="0" headerRowDxfId="57" dataDxfId="55" headerRowBorderDxfId="56" tableBorderDxfId="54">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{921EB506-3A8A-4A0B-B4FB-962E1B230FC8}" name="Students" displayName="Students" ref="B5:F6" insertRow="1" totalsRowShown="0" headerRowDxfId="60" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57">
   <autoFilter ref="B5:F6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{D3B37E7D-9062-40D6-B2B2-0A50D2AF30D8}" name="First name" dataDxfId="53"/>
-    <tableColumn id="3" xr3:uid="{DA765E80-CB03-496C-AB85-04C12F7F6EA1}" name="Last name" dataDxfId="52"/>
-    <tableColumn id="14" xr3:uid="{59DCAFC2-89B1-4CB1-9CF4-2945D31AD0A7}" name="Payer name" dataDxfId="51"/>
-    <tableColumn id="10" xr3:uid="{1186A2E8-3B8B-4232-BAAC-F12E28103DE4}" name="Id" dataDxfId="50"/>
-    <tableColumn id="11" xr3:uid="{2C87B7EC-1CBC-4BF1-BC1B-A80BEE6DF561}" name="PayerId" dataDxfId="49"/>
+    <tableColumn id="2" xr3:uid="{D3B37E7D-9062-40D6-B2B2-0A50D2AF30D8}" name="First name" dataDxfId="56"/>
+    <tableColumn id="3" xr3:uid="{DA765E80-CB03-496C-AB85-04C12F7F6EA1}" name="Last name" dataDxfId="55"/>
+    <tableColumn id="14" xr3:uid="{59DCAFC2-89B1-4CB1-9CF4-2945D31AD0A7}" name="Payer name" dataDxfId="54"/>
+    <tableColumn id="10" xr3:uid="{1186A2E8-3B8B-4232-BAAC-F12E28103DE4}" name="Id" dataDxfId="53"/>
+    <tableColumn id="11" xr3:uid="{2C87B7EC-1CBC-4BF1-BC1B-A80BEE6DF561}" name="PayerId" dataDxfId="52"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AD4BFF54-6050-4EA0-B5EE-4251BB923ED8}" name="Specifications" displayName="Specifications" ref="B5:K6" insertRow="1" totalsRowShown="0" headerRowDxfId="48" dataDxfId="46" headerRowBorderDxfId="47" tableBorderDxfId="45">
-  <autoFilter ref="B5:K6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{A984BEB5-CD0A-4CBC-8261-5202F875C894}" name="Name" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{E5D86B37-BC1B-421B-8F67-1924F653B36B}" name="Student name" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{4F31CB14-2A08-4670-A72E-704E0461B7C0}" name="Service" dataDxfId="42"/>
-    <tableColumn id="14" xr3:uid="{2046F612-0B54-4B4A-8FFD-EC5D6AB309E9}" name="Duration" dataDxfId="41"/>
-    <tableColumn id="15" xr3:uid="{3B56031F-69EE-48E1-914B-517D98BD2AF6}" name="Price" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{4CB3842E-EB1D-45CA-9308-72C92977B251}" name="Online" dataDxfId="39"/>
-    <tableColumn id="4" xr3:uid="{E7ED6501-C9FE-4D56-95A1-F6238FF1D18F}" name="Weekend" dataDxfId="38"/>
-    <tableColumn id="10" xr3:uid="{AC948A85-76D1-41F8-8643-7143CFC6B853}" name="ID" dataDxfId="37"/>
-    <tableColumn id="16" xr3:uid="{97831813-DA71-41F9-9C8D-B5BDF0ABEBAF}" name="Student ID" dataDxfId="36"/>
-    <tableColumn id="11" xr3:uid="{CF31A15E-2BAA-48FB-B0FE-4AE64ECEA47C}" name="Service ID" dataDxfId="35"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{AD4BFF54-6050-4EA0-B5EE-4251BB923ED8}" name="Specifications" displayName="Specifications" ref="B5:L6" insertRow="1" totalsRowShown="0" headerRowDxfId="51" dataDxfId="49" headerRowBorderDxfId="50" tableBorderDxfId="48">
+  <autoFilter ref="B5:L6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{A984BEB5-CD0A-4CBC-8261-5202F875C894}" name="Name" dataDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{E5D86B37-BC1B-421B-8F67-1924F653B36B}" name="Student name" dataDxfId="46"/>
+    <tableColumn id="3" xr3:uid="{4F31CB14-2A08-4670-A72E-704E0461B7C0}" name="Service" dataDxfId="45"/>
+    <tableColumn id="14" xr3:uid="{2046F612-0B54-4B4A-8FFD-EC5D6AB309E9}" name="Duration" dataDxfId="44"/>
+    <tableColumn id="15" xr3:uid="{3B56031F-69EE-48E1-914B-517D98BD2AF6}" name="Price" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{4CB3842E-EB1D-45CA-9308-72C92977B251}" name="Online" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{E7ED6501-C9FE-4D56-95A1-F6238FF1D18F}" name="Weekend" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{9253E908-3CAE-4F64-B5A8-B2F87F28BA64}" name="Usage" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{AC948A85-76D1-41F8-8643-7143CFC6B853}" name="ID" dataDxfId="40"/>
+    <tableColumn id="16" xr3:uid="{97831813-DA71-41F9-9C8D-B5BDF0ABEBAF}" name="Student ID" dataDxfId="39"/>
+    <tableColumn id="11" xr3:uid="{CF31A15E-2BAA-48FB-B0FE-4AE64ECEA47C}" name="Service ID" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}" name="Lessons" displayName="Lessons" ref="B5:R6" insertRow="1" totalsRowShown="0" headerRowDxfId="34" dataDxfId="32" headerRowBorderDxfId="33" tableBorderDxfId="31">
-  <autoFilter ref="B5:R6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
-  <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{C1CFA75B-DE21-4250-99D5-6D2B34197E9D}" name="Date" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{E13660C3-AD05-4CF3-9631-AE40C9F89101}" name="Service" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{18BEE297-19DF-4B3B-B4FD-CFAE8F7A6949}" name="Student" dataDxfId="28"/>
-    <tableColumn id="18" xr3:uid="{856AA0AD-A9D2-4BC4-B64C-DD339BB060A4}" name="Final Price" dataDxfId="27"/>
-    <tableColumn id="19" xr3:uid="{F88A226A-165B-497E-A103-652D51B5F335}" name="Paid" dataDxfId="26"/>
-    <tableColumn id="20" xr3:uid="{F2CC646E-5F4F-4968-901D-FB64DDD94A6C}" name="Notes" dataDxfId="25"/>
-    <tableColumn id="9" xr3:uid="{8F080EB1-2903-456C-965B-2C7056063FA0}" name="Bill" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{6C9740E9-87C2-4CC6-9AAD-1D8340BBB1E2}" name="Price / hour" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{6CA1B731-8C2F-4DA6-B472-EE33DF6113CD}" name="Duration (min)" dataDxfId="22"/>
-    <tableColumn id="8" xr3:uid="{7A134DA8-4763-4978-90B3-711AAD8B520E}" name="Base price" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{7DCD903B-2C97-4AD2-B1F7-E4B6242A2CC8}" name="Online" dataDxfId="20"/>
-    <tableColumn id="14" xr3:uid="{E380BC68-97E8-4AEA-AEA7-229CB9BBE907}" name="Travel allowance" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{96F08C18-13F5-448F-99C8-A2B2DE97A9B4}" name="Weekend" dataDxfId="18"/>
-    <tableColumn id="15" xr3:uid="{E1686B38-6591-41DA-BC53-FA0A75D72633}" name="Weekend Fee" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{08B3198D-C1DC-4D8E-A4DE-7250D3A7C710}" name="Lesson ID" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{D13F67C3-A32E-454C-AE4D-C716888F27CB}" name="Student ID" dataDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{9B183B96-B338-4F28-AD14-AC6E651B6858}" name="Bill ID" dataDxfId="14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}" name="Lessons" displayName="Lessons" ref="B5:S6" insertRow="1" totalsRowShown="0" headerRowDxfId="37" dataDxfId="35" headerRowBorderDxfId="36" tableBorderDxfId="34">
+  <autoFilter ref="B5:S6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
+  <tableColumns count="18">
+    <tableColumn id="1" xr3:uid="{C1CFA75B-DE21-4250-99D5-6D2B34197E9D}" name="Date" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{E13660C3-AD05-4CF3-9631-AE40C9F89101}" name="Service" dataDxfId="32"/>
+    <tableColumn id="4" xr3:uid="{18BEE297-19DF-4B3B-B4FD-CFAE8F7A6949}" name="Student" dataDxfId="31"/>
+    <tableColumn id="18" xr3:uid="{856AA0AD-A9D2-4BC4-B64C-DD339BB060A4}" name="Final Price" dataDxfId="30"/>
+    <tableColumn id="19" xr3:uid="{F88A226A-165B-497E-A103-652D51B5F335}" name="Paid" dataDxfId="29"/>
+    <tableColumn id="20" xr3:uid="{F2CC646E-5F4F-4968-901D-FB64DDD94A6C}" name="Notes" dataDxfId="28"/>
+    <tableColumn id="9" xr3:uid="{8F080EB1-2903-456C-965B-2C7056063FA0}" name="Bill" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{6C9740E9-87C2-4CC6-9AAD-1D8340BBB1E2}" name="Price / hour" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{6CA1B731-8C2F-4DA6-B472-EE33DF6113CD}" name="Duration (min)" dataDxfId="25"/>
+    <tableColumn id="8" xr3:uid="{7A134DA8-4763-4978-90B3-711AAD8B520E}" name="Base price" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{7DCD903B-2C97-4AD2-B1F7-E4B6242A2CC8}" name="Online" dataDxfId="23"/>
+    <tableColumn id="14" xr3:uid="{E380BC68-97E8-4AEA-AEA7-229CB9BBE907}" name="Travel allowance" dataDxfId="22"/>
+    <tableColumn id="7" xr3:uid="{96F08C18-13F5-448F-99C8-A2B2DE97A9B4}" name="Weekend" dataDxfId="21"/>
+    <tableColumn id="15" xr3:uid="{E1686B38-6591-41DA-BC53-FA0A75D72633}" name="Weekend Fee" dataDxfId="20"/>
+    <tableColumn id="13" xr3:uid="{FD6DAC84-1316-4CAE-AA51-82ADB0D93933}" name="Tip" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{08B3198D-C1DC-4D8E-A4DE-7250D3A7C710}" name="Lesson ID" dataDxfId="19"/>
+    <tableColumn id="11" xr3:uid="{D13F67C3-A32E-454C-AE4D-C716888F27CB}" name="Student ID" dataDxfId="18"/>
+    <tableColumn id="12" xr3:uid="{9B183B96-B338-4F28-AD14-AC6E651B6858}" name="Bill ID" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C992FC1D-929F-4FCC-8034-BD1DE7AB4724}" name="Bills" displayName="Bills" ref="B5:H6" insertRow="1" totalsRowShown="0" headerRowDxfId="87" dataDxfId="85" headerRowBorderDxfId="86" tableBorderDxfId="84">
-  <autoFilter ref="B5:H6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{C69805C5-2DE6-4F5E-8595-BD91192122FB}" name="Name" dataDxfId="83"/>
-    <tableColumn id="2" xr3:uid="{31887EF0-F959-496C-8E82-BFC9313A5BD4}" name="Type" dataDxfId="82"/>
-    <tableColumn id="3" xr3:uid="{BD335C6E-9933-48E1-94D0-D0E510EFF5FB}" name="Created UTC" dataDxfId="81"/>
-    <tableColumn id="4" xr3:uid="{899EB7AE-2A40-41FC-80B1-65CB3A3ADF6E}" name="Payer" dataDxfId="80"/>
-    <tableColumn id="6" xr3:uid="{BB6B6371-F4F3-4ED2-B36B-8B9F19FEC62D}" name="Total" dataDxfId="79"/>
-    <tableColumn id="12" xr3:uid="{8DFC1E1F-49ED-490A-A022-750D97F2DB5E}" name="Payer ID" dataDxfId="78"/>
-    <tableColumn id="13" xr3:uid="{B0BEC736-D1AC-4A3A-A050-D3DA3F256C81}" name="ID" dataDxfId="77"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C992FC1D-929F-4FCC-8034-BD1DE7AB4724}" name="Bills" displayName="Bills" ref="B5:I6" insertRow="1" totalsRowShown="0" headerRowDxfId="90" dataDxfId="88" headerRowBorderDxfId="89" tableBorderDxfId="87">
+  <autoFilter ref="B5:I6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{C69805C5-2DE6-4F5E-8595-BD91192122FB}" name="Name" dataDxfId="86"/>
+    <tableColumn id="2" xr3:uid="{31887EF0-F959-496C-8E82-BFC9313A5BD4}" name="Type" dataDxfId="85"/>
+    <tableColumn id="3" xr3:uid="{BD335C6E-9933-48E1-94D0-D0E510EFF5FB}" name="Created UTC" dataDxfId="84"/>
+    <tableColumn id="4" xr3:uid="{899EB7AE-2A40-41FC-80B1-65CB3A3ADF6E}" name="Payer" dataDxfId="83"/>
+    <tableColumn id="6" xr3:uid="{BB6B6371-F4F3-4ED2-B36B-8B9F19FEC62D}" name="Total" dataDxfId="82"/>
+    <tableColumn id="12" xr3:uid="{8DFC1E1F-49ED-490A-A022-750D97F2DB5E}" name="Payer ID" dataDxfId="81"/>
+    <tableColumn id="13" xr3:uid="{B0BEC736-D1AC-4A3A-A050-D3DA3F256C81}" name="ID" dataDxfId="80"/>
+    <tableColumn id="5" xr3:uid="{D6452AA6-9AAA-4EB7-9676-1AB575F8BFA3}" name="Sequence" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A2CA2C87-2B1E-47CC-B98B-F6DB30254282}" name="Profiles" displayName="Profiles" ref="B5:K6" insertRow="1" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A2CA2C87-2B1E-47CC-B98B-F6DB30254282}" name="Profiles" displayName="Profiles" ref="B5:K6" insertRow="1" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13">
   <autoFilter ref="B5:K6" xr:uid="{03081AB8-5B53-403B-BC5F-49AB53C274F2}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{2F7003BC-BC4F-49D1-8191-9B7B77A95DAD}" name="Full name" dataDxfId="9"/>
-    <tableColumn id="17" xr3:uid="{1ED8C0D8-B8BF-4CB8-BF2A-11954C2F7E1C}" name="Zip code" dataDxfId="8"/>
-    <tableColumn id="20" xr3:uid="{7DBD046D-D51C-4C4F-8604-D6DEC2103E43}" name="City" dataDxfId="7"/>
-    <tableColumn id="19" xr3:uid="{7D393146-6466-4F51-87B6-10B7C5614A6A}" name="Phone" dataDxfId="6"/>
-    <tableColumn id="18" xr3:uid="{C771F655-E405-4BB5-AD39-3D5A94E1BBE0}" name="CIF/NIF" dataDxfId="5"/>
-    <tableColumn id="23" xr3:uid="{0F800687-A552-4911-A84F-66F27E40B2E9}" name="Email" dataDxfId="4"/>
-    <tableColumn id="22" xr3:uid="{2B05B060-5CA2-4293-8190-C4310A9D436E}" name="Bank name" dataDxfId="3"/>
-    <tableColumn id="21" xr3:uid="{7D5301B1-5635-4EF9-88C0-B2D2B15286FD}" name="Bank account" dataDxfId="2"/>
-    <tableColumn id="24" xr3:uid="{9790EA57-CF62-4EF2-ACAE-3D1545D8BFD5}" name="IVA" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{FAC1AFDA-6CB4-4B8D-A36E-7D10AC1588CA}" name="Address" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{2F7003BC-BC4F-49D1-8191-9B7B77A95DAD}" name="Full name" dataDxfId="12"/>
+    <tableColumn id="17" xr3:uid="{1ED8C0D8-B8BF-4CB8-BF2A-11954C2F7E1C}" name="Zip code" dataDxfId="11"/>
+    <tableColumn id="20" xr3:uid="{7DBD046D-D51C-4C4F-8604-D6DEC2103E43}" name="City" dataDxfId="10"/>
+    <tableColumn id="19" xr3:uid="{7D393146-6466-4F51-87B6-10B7C5614A6A}" name="Phone" dataDxfId="9"/>
+    <tableColumn id="18" xr3:uid="{C771F655-E405-4BB5-AD39-3D5A94E1BBE0}" name="CIF/NIF" dataDxfId="8"/>
+    <tableColumn id="23" xr3:uid="{0F800687-A552-4911-A84F-66F27E40B2E9}" name="Email" dataDxfId="7"/>
+    <tableColumn id="22" xr3:uid="{2B05B060-5CA2-4293-8190-C4310A9D436E}" name="Bank name" dataDxfId="6"/>
+    <tableColumn id="21" xr3:uid="{7D5301B1-5635-4EF9-88C0-B2D2B15286FD}" name="Bank account" dataDxfId="5"/>
+    <tableColumn id="24" xr3:uid="{9790EA57-CF62-4EF2-ACAE-3D1545D8BFD5}" name="IVA" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{FAC1AFDA-6CB4-4B8D-A36E-7D10AC1588CA}" name="Address" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2391,7 +2459,7 @@
     </row>
     <row r="3" spans="1:6" ht="34.5" x14ac:dyDescent="0.45">
       <c r="B3" s="20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" s="21"/>
     </row>
@@ -2409,7 +2477,7 @@
         <v>17</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E5" s="15" t="s">
         <v>14</v>
@@ -2497,7 +2565,7 @@
         <v>28</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="H5" s="15" t="s">
         <v>14</v>
@@ -2616,7 +2684,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D59E97CD-50F3-44EA-A57D-8B54153DA60F}">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="2" customWidth="1"/>
@@ -2625,13 +2693,13 @@
     <col min="4" max="6" width="31.28515625" style="2" customWidth="1"/>
     <col min="7" max="7" width="23.7109375" style="2" customWidth="1"/>
     <col min="8" max="8" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.85546875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="2"/>
+    <col min="9" max="10" width="12.85546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.140625" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -2639,7 +2707,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
-    <row r="3" spans="1:12" ht="34.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" ht="34.5" x14ac:dyDescent="0.45">
       <c r="B3" s="20" t="s">
         <v>23</v>
       </c>
@@ -2649,7 +2717,7 @@
       <c r="F3" s="21"/>
       <c r="G3" s="21"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -2659,8 +2727,9 @@
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K4" s="3"/>
+    </row>
+    <row r="5" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="6" t="s">
         <v>2</v>
@@ -2681,20 +2750,23 @@
         <v>7</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="I5" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="K5" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="L5" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="L5" s="5"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M5" s="5"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2703,11 +2775,12 @@
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
-      <c r="I6" s="14"/>
+      <c r="I6" s="8"/>
       <c r="J6" s="14"/>
-      <c r="K6" s="7"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K6" s="14"/>
+      <c r="L6" s="7"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -2728,7 +2801,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B8EF7-62DE-4FCD-B8E3-460BB4D2C6F0}">
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="2" customWidth="1"/>
@@ -2745,14 +2818,14 @@
     <col min="12" max="12" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" style="2"/>
-    <col min="16" max="16" width="14.140625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="9.140625" style="2"/>
-    <col min="18" max="18" width="15.42578125" style="2" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="2"/>
+    <col min="15" max="16" width="9.140625" style="2"/>
+    <col min="17" max="17" width="14.140625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.140625" style="2"/>
+    <col min="19" max="19" width="15.42578125" style="2" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -2763,7 +2836,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="3" spans="1:19" ht="34.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:20" ht="34.5" x14ac:dyDescent="0.45">
       <c r="B3" s="20" t="s">
         <v>0</v>
       </c>
@@ -2773,7 +2846,7 @@
       <c r="F3" s="21"/>
       <c r="G3" s="22"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -2788,8 +2861,9 @@
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
-    </row>
-    <row r="5" spans="1:19" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P4" s="3"/>
+    </row>
+    <row r="5" spans="1:20" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="6" t="s">
         <v>1</v>
@@ -2801,50 +2875,53 @@
         <v>3</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J5" s="19" t="s">
         <v>6</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L5" s="19" t="s">
         <v>7</v>
       </c>
       <c r="M5" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="N5" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="O5" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="N5" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="O5" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="P5" s="18" t="s">
+      <c r="P5" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q5" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="15" t="s">
+      <c r="R5" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="R5" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="S5" s="5"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="S5" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="T5" s="5"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="9"/>
       <c r="C6" s="10"/>
@@ -2860,11 +2937,12 @@
       <c r="M6" s="8"/>
       <c r="N6" s="8"/>
       <c r="O6" s="8"/>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="7"/>
+      <c r="P6" s="8"/>
+      <c r="Q6" s="14"/>
       <c r="R6" s="7"/>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="S6" s="7"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -2933,24 +3011,26 @@
         <v>2</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F5" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H5" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="5"/>
+      <c r="I5" s="15" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
@@ -2961,6 +3041,7 @@
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
+      <c r="I6" s="25"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" s="7"/>
@@ -3006,7 +3087,7 @@
     </row>
     <row r="3" spans="1:12" ht="34.5" x14ac:dyDescent="0.45">
       <c r="B3" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
@@ -3033,7 +3114,7 @@
     <row r="5" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>27</v>
@@ -3042,22 +3123,22 @@
         <v>28</v>
       </c>
       <c r="E5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="I5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="J5" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="K5" s="6" t="s">
         <v>26</v>
